--- a/output/1 - controls/controls_output.xlsx
+++ b/output/1 - controls/controls_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,15 +449,20 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>extraction_source</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>applicability</t>
         </is>
@@ -484,15 +489,17 @@
           <t>Users shall not install, download, or execute software that has not been approved by IT. Refer to Section 2.2 of the Configuration Management Policy (Control CFG04.001) for the software inventory management requirements and CFG04.002 for application whitelisting requirements.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>This policy defines the acceptable use of organizational information technology resources, including computers, networks, email, internet access, mobile devices, and cloud services. The purpose is to protect organizational assets, data, and reputation while enabling personnel to perform their duties effectively.</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>This policy applies to all personnel who access organizational IT resources, including full-time employees, part-time employees, contractors, interns, volunteers, and temporary staff. It covers all devices and systems, whether owned by the organization or personally owned devices used for organizational purposes (BYOD). For BYOD-specific requirements, refer to Section 4.3 of the Mobile Device Management Policy.</t>
         </is>
@@ -519,17 +526,6100 @@
           <t>Users shall not install, download, or execute software that has not been approved by IT. Refer to Section 2.2 of the Configuration Management Policy (Control CFG04.001) for the software inventory management requirements and CFG04.002 for application whitelisting requirements.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>This policy defines the acceptable use of organizational information technology resources, including computers, networks, email, internet access, mobile devices, and cloud services. The purpose is to protect organizational assets, data, and reputation while enabling personnel to perform their duties effectively.</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>This policy applies to all personnel who access organizational IT resources, including full-time employees, part-time employees, contractors, interns, volunteers, and temporary staff. It covers all devices and systems, whether owned by the organization or personally owned devices used for organizational purposes (BYOD). For BYOD-specific requirements, refer to Section 4.3 of the Mobile Device Management Policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Acceptable_Use_Policy_POL-AU-2026-006.docx</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Appendix</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AUP 1.001</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AUP 1.001 Users shall complete acceptable use training within 30 days of onboarding and annually thereafter. PL-4</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>This policy defines the acceptable use of organizational information technology resources, including computers, networks, email, internet access, mobile devices, and cloud services. The purpose is to protect organizational assets, data, and reputation while enabling personnel to perform their duties effectively.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>This policy applies to all personnel who access organizational IT resources, including full-time employees, part-time employees, contractors, interns, volunteers, and temporary staff. It covers all devices and systems, whether owned by the organization or personally owned devices used for organizational purposes (BYOD). For BYOD-specific requirements, refer to Section 4.3 of the Mobile Device Management Policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Acceptable_Use_Policy_POL-AU-2026-006.docx</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Appendix</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AUP 1.002</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AUP 1.002 Users shall sign an acceptable use agreement before being granted access to organizational systems. PL-4(1)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>This policy defines the acceptable use of organizational information technology resources, including computers, networks, email, internet access, mobile devices, and cloud services. The purpose is to protect organizational assets, data, and reputation while enabling personnel to perform their duties effectively.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>This policy applies to all personnel who access organizational IT resources, including full-time employees, part-time employees, contractors, interns, volunteers, and temporary staff. It covers all devices and systems, whether owned by the organization or personally owned devices used for organizational purposes (BYOD). For BYOD-specific requirements, refer to Section 4.3 of the Mobile Device Management Policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Acceptable_Use_Policy_POL-AU-2026-006.docx</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Appendix</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AUP 2.001</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AUP 2.001 Organizational systems shall display a login banner stating that use constitutes consent to monitoring. AC-8</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>This policy defines the acceptable use of organizational information technology resources, including computers, networks, email, internet access, mobile devices, and cloud services. The purpose is to protect organizational assets, data, and reputation while enabling personnel to perform their duties effectively.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>This policy applies to all personnel who access organizational IT resources, including full-time employees, part-time employees, contractors, interns, volunteers, and temporary staff. It covers all devices and systems, whether owned by the organization or personally owned devices used for organizational purposes (BYOD). For BYOD-specific requirements, refer to Section 4.3 of the Mobile Device Management Policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Access_Control_Policy_POL-AC-2026-001.docx</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Appendix B - Revision History</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ACC01.001</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ACC01.001 User Account Provisioning All user accounts shall be provisioned through the centralized identity management system with documented approval from the data owner. AC-2 Implemented IT Security</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>This policy establishes the access control requirements for all information systems operated by the organization. The intent is to ensure that only authorized personnel can access sensitive data and systems in accordance with the principle of least privilege.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>This policy applies to all employees, contractors, and third-party personnel who access organizational information systems. For additional personnel categories, refer to Section 4 of this document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Access_Control_Policy_POL-AC-2026-001.docx</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Appendix B - Revision History</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ACC01.002</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ACC01.002 Privileged Account Management Privileged accounts shall be reviewed quarterly and require multi-factor authentication for all access. Refer to Section 4.3 for MFA requirements. AC-6 Implemented IT Security</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>This policy establishes the access control requirements for all information systems operated by the organization. The intent is to ensure that only authorized personnel can access sensitive data and systems in accordance with the principle of least privilege.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>This policy applies to all employees, contractors, and third-party personnel who access organizational information systems. For additional personnel categories, refer to Section 4 of this document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Access_Control_Policy_POL-AC-2026-001.docx</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Appendix B - Revision History</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ACC02.001</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ACC02.001 Remote Access Controls Remote access shall be permitted only through approved VPN connections with certificate-based authentication. AC-17 Implemented Network Ops</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>This policy establishes the access control requirements for all information systems operated by the organization. The intent is to ensure that only authorized personnel can access sensitive data and systems in accordance with the principle of least privilege.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>This policy applies to all employees, contractors, and third-party personnel who access organizational information systems. For additional personnel categories, refer to Section 4 of this document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Access_Control_Policy_POL-AC-2026-001.docx</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Appendix B - Revision History</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ACC02.002</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ACC02.002 Wireless Access Restrictions Wireless network access for organizational devices shall require 802.1X authentication. See the Network Security Policy, Section 3.1 for wireless architecture. AC-18 Partially Implemented Network Ops</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>This policy establishes the access control requirements for all information systems operated by the organization. The intent is to ensure that only authorized personnel can access sensitive data and systems in accordance with the principle of least privilege.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>This policy applies to all employees, contractors, and third-party personnel who access organizational information systems. For additional personnel categories, refer to Section 4 of this document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Access_Control_Policy_POL-AC-2026-001.docx</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Appendix B - Revision History</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ACC03.001</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ACC03.001 Session Lock Requirements Information systems shall enforce session lock after 15 minutes of inactivity as described in Section 2.4 above. AC-11 Implemented Endpoint Team</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>This policy establishes the access control requirements for all information systems operated by the organization. The intent is to ensure that only authorized personnel can access sensitive data and systems in accordance with the principle of least privilege.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>This policy applies to all employees, contractors, and third-party personnel who access organizational information systems. For additional personnel categories, refer to Section 4 of this document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Access_Control_Policy_POL-AC-2026-001.docx</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Appendix B - Revision History</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ACC03.002</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ACC03.002 Session Termination Sessions shall be automatically terminated after 8 hours of continuous use. AC-12 Not Implemented Endpoint Team Req ID Description Framework Ref</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>This policy establishes the access control requirements for all information systems operated by the organization. The intent is to ensure that only authorized personnel can access sensitive data and systems in accordance with the principle of least privilege.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>This policy applies to all employees, contractors, and third-party personnel who access organizational information systems. For additional personnel categories, refer to Section 4 of this document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Access_Control_Policy_POL-AC-2026-001.docx</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Appendix B - Revision History</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SAR01.001</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SAR01.001 CUI systems shall implement role-based access control (RBAC) with documented role definitions reviewed annually. NIST AC-3</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>This policy establishes the access control requirements for all information systems operated by the organization. The intent is to ensure that only authorized personnel can access sensitive data and systems in accordance with the principle of least privilege.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>This policy applies to all employees, contractors, and third-party personnel who access organizational information systems. For additional personnel categories, refer to Section 4 of this document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Access_Control_Policy_POL-AC-2026-001.docx</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Appendix B - Revision History</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SAR01.002</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SAR01.002 Access to CUI shall be logged and audit trails retained for a minimum of 3 years per the Records Retention Policy.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>This policy establishes the access control requirements for all information systems operated by the organization. The intent is to ensure that only authorized personnel can access sensitive data and systems in accordance with the principle of least privilege.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>This policy applies to all employees, contractors, and third-party personnel who access organizational information systems. For additional personnel categories, refer to Section 4 of this document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Access_Control_Policy_POL-AC-2026-001.docx</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NIST AC-4, AU-3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SAR02.001</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SAR02.001 External connections to CUI systems require authorization from the ISSM. As previously stated in Section 3, all remote access must use the approved VPN. NIST AC-4 Term Definition Least Privilege The principle that users should be granted only the minimum access necessary to perform their job functions. MFA Multi-Factor Authentication. A security mechanism requiring two or more verification factors. RBAC Role-Based Access Control. Access permissions assigned based on organizational roles. CUI Controlled Unclassified Information. Information the Government creates or possesses that requires safeguarding. Version Date Author Changes 3.2 01/15/2026 J. Smith, CISO Added CUI supplementary requirements 3.1 07/01/2025 J. Smith, CISO Updated MFA requirements per new NIST guidance 3.0 01/15/2025 M. Johnson Major revision for FedRAMP alignment</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>This policy establishes the access control requirements for all information systems operated by the organization. The intent is to ensure that only authorized personnel can access sensitive data and systems in accordance with the principle of least privilege.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>This policy applies to all employees, contractors, and third-party personnel who access organizational information systems. For additional personnel categories, refer to Section 4 of this document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Configuration_Management_Policy_POL-CM-2026-004.docx</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Appendix - Framework Crosswalk</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CFG01.001</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CFG01.001 Security Baseline Development The organization shall develop and maintain security configuration baselines for all system types (servers, workstations, network devices) based on CIS Benchmarks or DISA STIGs. CM-2 Implemented Security Engineering</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Policy Purpose This document establishes the configuration management requirements for all information systems and network devices operated by the organization. Configuration management ensures that systems remain in a known, secure state throughout their lifecycle.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Policy Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Configuration_Management_Policy_POL-CM-2026-004.docx</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Appendix - Framework Crosswalk</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CFG01.002</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CFG01.002 Baseline Review Cycle Configuration baselines shall be reviewed and updated at least annually or when significant changes occur to the threat landscape. See the Continuous Monitoring Policy for threat assessment frequency. CM-2(1) Implemented Security Engineering</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Policy Purpose This document establishes the configuration management requirements for all information systems and network devices operated by the organization. Configuration management ensures that systems remain in a known, secure state throughout their lifecycle.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Policy Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Configuration_Management_Policy_POL-CM-2026-004.docx</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Appendix - Framework Crosswalk</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CFG02.001</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CFG02.001 Change Control Process All configuration changes shall be submitted through the change advisory board (CAB) process. Emergency changes require post-implementation review within 48 hours. CM-3 Implemented Change Management</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Policy Purpose This document establishes the configuration management requirements for all information systems and network devices operated by the organization. Configuration management ensures that systems remain in a known, secure state throughout their lifecycle.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Policy Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Configuration_Management_Policy_POL-CM-2026-004.docx</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Appendix - Framework Crosswalk</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CFG02.002</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CFG02.002 Change Impact Analysis Configuration changes shall include a documented security impact analysis prior to approval. Refer to Section 4 of this document for the impact analysis template. CM-4 Partially Implemented Security Engineering Control ID Title Description NIST Mapping Implementation Status Responsible Party</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Policy Purpose This document establishes the configuration management requirements for all information systems and network devices operated by the organization. Configuration management ensures that systems remain in a known, secure state throughout their lifecycle.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Policy Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Configuration_Management_Policy_POL-CM-2026-004.docx</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Appendix - Framework Crosswalk</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CFG03.001</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CFG03.001 Automated Configuration Scanning Systems shall be scanned for configuration compliance at least weekly using automated tools. Non-compliant systems shall be flagged for remediation. CM-6 Implemented Security Operations</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Policy Purpose This document establishes the configuration management requirements for all information systems and network devices operated by the organization. Configuration management ensures that systems remain in a known, secure state throughout their lifecycle.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Policy Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Configuration_Management_Policy_POL-CM-2026-004.docx</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Appendix - Framework Crosswalk</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CFG03.002</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CFG03.002 Configuration Drift Detection The organization shall deploy automated drift detection that alerts when system configurations deviate from the approved baseline. CM-3(5) Not Implemented Security Operations</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Policy Purpose This document establishes the configuration management requirements for all information systems and network devices operated by the organization. Configuration management ensures that systems remain in a known, secure state throughout their lifecycle.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Policy Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Configuration_Management_Policy_POL-CM-2026-004.docx</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Appendix - Framework Crosswalk</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CFG04.001</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CFG04.001 Software Inventory Management The organization shall maintain an automated inventory of all installed software. Unauthorized software shall be removed within 72 hours of detection. CM-7 Partially Implemented Endpoint Management</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Policy Purpose This document establishes the configuration management requirements for all information systems and network devices operated by the organization. Configuration management ensures that systems remain in a known, secure state throughout their lifecycle.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Policy Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Configuration_Management_Policy_POL-CM-2026-004.docx</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Appendix - Framework Crosswalk</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CFG04.002</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CFG04.002 Application Whitelisting Critical systems shall implement application whitelisting to prevent execution of unauthorized software. As previously stated, unauthorized software must be removed within 72 hours. CM-7(5) Not Implemented Endpoint Management Role Responsibilities CISO Approves configuration baselines. Authorizes exceptions. Reviews compliance reports quarterly. Security Engineering Develops and maintains baselines. Conducts security impact analyses. Refer to Section 2.1 for baseline development controls. Change Management Operates the CAB. Documents change requests. Tracks implementation status. Security Operations Executes configuration scans. Reports drift. Coordinates remediation with system owners. System Owners Maintain system compliance with baselines. Submit change requests. Respond to scan findings within SLA. Analysis Element Required Information Change Description Detailed technical description of the proposed change. Systems Affected List all systems, applications, and network segments impacted. Security Impact Assessment of how the change affects the security posture. Does it alter the baseline? Does it introduce new ports, protocols, or services? Rollback Plan Documented procedure to reverse the change if issues arise. Testing Results Evidence from test/staging environment. See the System Development Policy, Section 6 for testing requirements. Org Control ID NIST 800-53 CIS Control FedRAMP Baseline</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Policy Purpose This document establishes the configuration management requirements for all information systems and network devices operated by the organization. Configuration management ensures that systems remain in a known, secure state throughout their lifecycle.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Policy Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Configuration_Management_Policy_POL-CM-2026-004.docx</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Appendix - Framework Crosswalk</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CFG01.001</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CFG01.001 CM-2 CIS 4.1 CM-2 (Moderate)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Policy Purpose This document establishes the configuration management requirements for all information systems and network devices operated by the organization. Configuration management ensures that systems remain in a known, secure state throughout their lifecycle.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Policy Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Configuration_Management_Policy_POL-CM-2026-004.docx</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Appendix - Framework Crosswalk</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CFG01.002</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CFG01.002 CM-2(1) CIS 4.2 CM-2(1) (Moderate)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Policy Purpose This document establishes the configuration management requirements for all information systems and network devices operated by the organization. Configuration management ensures that systems remain in a known, secure state throughout their lifecycle.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Policy Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Configuration_Management_Policy_POL-CM-2026-004.docx</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Appendix - Framework Crosswalk</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CFG02.001</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CFG02.001 CM-3 CIS 4.8 CM-3 (Moderate)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Policy Purpose This document establishes the configuration management requirements for all information systems and network devices operated by the organization. Configuration management ensures that systems remain in a known, secure state throughout their lifecycle.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Policy Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Configuration_Management_Policy_POL-CM-2026-004.docx</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Appendix - Framework Crosswalk</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CFG02.002</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CFG02.002 CM-4 CIS 4.8 CM-4 (Moderate)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Policy Purpose This document establishes the configuration management requirements for all information systems and network devices operated by the organization. Configuration management ensures that systems remain in a known, secure state throughout their lifecycle.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Policy Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Configuration_Management_Policy_POL-CM-2026-004.docx</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Appendix - Framework Crosswalk</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CFG03.001</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CFG03.001 CM-6 CIS 4.1 CM-6 (Moderate)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Policy Purpose This document establishes the configuration management requirements for all information systems and network devices operated by the organization. Configuration management ensures that systems remain in a known, secure state throughout their lifecycle.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Policy Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Configuration_Management_Policy_POL-CM-2026-004.docx</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Appendix - Framework Crosswalk</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CFG03.002</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CFG03.002 CM-3(5) CIS 4.3 CM-3(5) (High)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Policy Purpose This document establishes the configuration management requirements for all information systems and network devices operated by the organization. Configuration management ensures that systems remain in a known, secure state throughout their lifecycle.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Policy Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Configuration_Management_Policy_POL-CM-2026-004.docx</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Appendix - Framework Crosswalk</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CFG04.001</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CFG04.001 CM-7 CIS 2.1 CM-7 (Moderate)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Policy Purpose This document establishes the configuration management requirements for all information systems and network devices operated by the organization. Configuration management ensures that systems remain in a known, secure state throughout their lifecycle.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Policy Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Configuration_Management_Policy_POL-CM-2026-004.docx</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Appendix - Framework Crosswalk</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CFG04.002</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CFG04.002 CM-7(5) CIS 2.6 CM-7(5) (High)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Policy Purpose This document establishes the configuration management requirements for all information systems and network devices operated by the organization. Configuration management ensures that systems remain in a known, secure state throughout their lifecycle.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Policy Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Continuous_Monitoring_Policy_POL-MON-2026-005.docx</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Intent</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>RMP02.001</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Static, point-in-time security assessments are insufficient for federal systems operating in a dynamic threat environment. The intent of this policy is to establish monitoring as a continuous operational function that supports timely detection of threats, configuration drift, and compliance deviations. Monitoring data shall directly inform risk register updates per the Risk Management Policy (POL-RM-2026-009), Control RMP02.001. This policy supports FISMA continuous monitoring requirements, OMB M-22-09 Zero Trust visibility requirements, and CDM program dashboard reporting obligations.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Static, point-in-time security assessments are insufficient for federal systems operating in a dynamic threat environment. The intent of this policy is to establish monitoring as a continuous operational function that supports timely detection of threats, configuration drift, and compliance deviations. Monitoring data shall directly inform risk register updates per the Risk Management Policy (POL-RM-2026-009), Control RMP02.001. This policy supports FISMA continuous monitoring requirements, OMB M-22-09 Zero Trust visibility requirements, and CDM program dashboard reporting obligations.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>This policy establishes the continuous monitoring requirements for all organizational information systems. It defines the frequency, scope, and response procedures for ongoing security assessments, vulnerability scanning, log analysis, and security metrics reporting. Continuous monitoring supports ongoing authorization and provides the ISSM and AO with near-real-time visibility into the security posture of organizational systems. This policy implements NIST SP 800-137 Information Security Continuous Monitoring guidance. For current CDM program requirements applicable to federal agencies, see CISA Continuous Diagnostics and Mitigation program.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational information systems operating under an Authority to Operate (ATO). It applies to system owners, ISSOs, the Security Operations Center, and all personnel with monitoring or logging responsibilities. Cloud service providers handling organizational data are subject to the monitoring requirements defined in their FedRAMP authorization boundaries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Continuous_Monitoring_Policy_POL-MON-2026-005.docx</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Section 3 - Vulnerability Management Controls</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MON01.001</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>MON01.001 - Authenticated Vulnerability Scanning Requirement: All systems shall undergo authenticated vulnerability scanning at minimum weekly for internet-facing systems and bi-weekly for internal systems. Scanning shall use an approved tool from Appendix B. Scans shall be credentialed to ensure complete coverage of installed software and configurations. Unauthenticated scans are not sufficient to satisfy this control. Scan schedules shall be documented in the system security plan (SSP). NIST Mapping: RA-5, RA-5(5) Status: Implemented Owner: Security Operations</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Static, point-in-time security assessments are insufficient for federal systems operating in a dynamic threat environment. The intent of this policy is to establish monitoring as a continuous operational function that supports timely detection of threats, configuration drift, and compliance deviations. Monitoring data shall directly inform risk register updates per the Risk Management Policy (POL-RM-2026-009), Control RMP02.001. This policy supports FISMA continuous monitoring requirements, OMB M-22-09 Zero Trust visibility requirements, and CDM program dashboard reporting obligations.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>This policy establishes the continuous monitoring requirements for all organizational information systems. It defines the frequency, scope, and response procedures for ongoing security assessments, vulnerability scanning, log analysis, and security metrics reporting. Continuous monitoring supports ongoing authorization and provides the ISSM and AO with near-real-time visibility into the security posture of organizational systems. This policy implements NIST SP 800-137 Information Security Continuous Monitoring guidance. For current CDM program requirements applicable to federal agencies, see CISA Continuous Diagnostics and Mitigation program.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational information systems operating under an Authority to Operate (ATO). It applies to system owners, ISSOs, the Security Operations Center, and all personnel with monitoring or logging responsibilities. Cloud service providers handling organizational data are subject to the monitoring requirements defined in their FedRAMP authorization boundaries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Continuous_Monitoring_Policy_POL-MON-2026-005.docx</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Section 3 - Vulnerability Management Controls</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MON01.002</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>MON01.002 - Vulnerability Remediation SLAs</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Static, point-in-time security assessments are insufficient for federal systems operating in a dynamic threat environment. The intent of this policy is to establish monitoring as a continuous operational function that supports timely detection of threats, configuration drift, and compliance deviations. Monitoring data shall directly inform risk register updates per the Risk Management Policy (POL-RM-2026-009), Control RMP02.001. This policy supports FISMA continuous monitoring requirements, OMB M-22-09 Zero Trust visibility requirements, and CDM program dashboard reporting obligations.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>This policy establishes the continuous monitoring requirements for all organizational information systems. It defines the frequency, scope, and response procedures for ongoing security assessments, vulnerability scanning, log analysis, and security metrics reporting. Continuous monitoring supports ongoing authorization and provides the ISSM and AO with near-real-time visibility into the security posture of organizational systems. This policy implements NIST SP 800-137 Information Security Continuous Monitoring guidance. For current CDM program requirements applicable to federal agencies, see CISA Continuous Diagnostics and Mitigation program.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational information systems operating under an Authority to Operate (ATO). It applies to system owners, ISSOs, the Security Operations Center, and all personnel with monitoring or logging responsibilities. Cloud service providers handling organizational data are subject to the monitoring requirements defined in their FedRAMP authorization boundaries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Continuous_Monitoring_Policy_POL-MON-2026-005.docx</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Section 3 - Vulnerability Management Controls</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>RMP03.001</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Requirement: Identified vulnerabilities shall be remediated within the following SLAs based on CVSS score: Critical (CVSS 9.0-10.0) within 15 calendar days; High (CVSS 7.0-8.9) within 30 days; Medium (CVSS 4.0-6.9) within 90 days; Low (CVSS 0.1-3.9) within 180 days. Exceptions require ISSM approval and a compensating control documented in a POA&amp;M entry per the Risk Management Policy, RMP03.001. See Appendix A for the severity matrix. NIST Mapping: RA-5(6), SI-2 Status: Implemented Owner: System Owners / Security Ops</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Static, point-in-time security assessments are insufficient for federal systems operating in a dynamic threat environment. The intent of this policy is to establish monitoring as a continuous operational function that supports timely detection of threats, configuration drift, and compliance deviations. Monitoring data shall directly inform risk register updates per the Risk Management Policy (POL-RM-2026-009), Control RMP02.001. This policy supports FISMA continuous monitoring requirements, OMB M-22-09 Zero Trust visibility requirements, and CDM program dashboard reporting obligations.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>This policy establishes the continuous monitoring requirements for all organizational information systems. It defines the frequency, scope, and response procedures for ongoing security assessments, vulnerability scanning, log analysis, and security metrics reporting. Continuous monitoring supports ongoing authorization and provides the ISSM and AO with near-real-time visibility into the security posture of organizational systems. This policy implements NIST SP 800-137 Information Security Continuous Monitoring guidance. For current CDM program requirements applicable to federal agencies, see CISA Continuous Diagnostics and Mitigation program.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational information systems operating under an Authority to Operate (ATO). It applies to system owners, ISSOs, the Security Operations Center, and all personnel with monitoring or logging responsibilities. Cloud service providers handling organizational data are subject to the monitoring requirements defined in their FedRAMP authorization boundaries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Continuous_Monitoring_Policy_POL-MON-2026-005.docx</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Section 4 - Log Management Controls</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MON02.001</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>MON02.001 - SIEM Log Ingestion and Correlation</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Static, point-in-time security assessments are insufficient for federal systems operating in a dynamic threat environment. The intent of this policy is to establish monitoring as a continuous operational function that supports timely detection of threats, configuration drift, and compliance deviations. Monitoring data shall directly inform risk register updates per the Risk Management Policy (POL-RM-2026-009), Control RMP02.001. This policy supports FISMA continuous monitoring requirements, OMB M-22-09 Zero Trust visibility requirements, and CDM program dashboard reporting obligations.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>This policy establishes the continuous monitoring requirements for all organizational information systems. It defines the frequency, scope, and response procedures for ongoing security assessments, vulnerability scanning, log analysis, and security metrics reporting. Continuous monitoring supports ongoing authorization and provides the ISSM and AO with near-real-time visibility into the security posture of organizational systems. This policy implements NIST SP 800-137 Information Security Continuous Monitoring guidance. For current CDM program requirements applicable to federal agencies, see CISA Continuous Diagnostics and Mitigation program.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational information systems operating under an Authority to Operate (ATO). It applies to system owners, ISSOs, the Security Operations Center, and all personnel with monitoring or logging responsibilities. Cloud service providers handling organizational data are subject to the monitoring requirements defined in their FedRAMP authorization boundaries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Continuous_Monitoring_Policy_POL-MON-2026-005.docx</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Section 4 - Log Management Controls</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>IRP02.001</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Requirement: All systems, network devices, and applications within the ATO boundary shall forward security-relevant logs to the organizational SIEM in real time or near-real-time (maximum 5-minute delay). Log format shall conform to the standards in Appendix C. The SOC shall validate log ingestion completeness daily. Gaps in log ingestion for critical systems shall generate a P2 alert per the Incident Response Policy, IRP02.001. NIST Mapping: AU-2, AU-9, SI-4 Status: Implemented Owner: SOC / Security Engineering</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Static, point-in-time security assessments are insufficient for federal systems operating in a dynamic threat environment. The intent of this policy is to establish monitoring as a continuous operational function that supports timely detection of threats, configuration drift, and compliance deviations. Monitoring data shall directly inform risk register updates per the Risk Management Policy (POL-RM-2026-009), Control RMP02.001. This policy supports FISMA continuous monitoring requirements, OMB M-22-09 Zero Trust visibility requirements, and CDM program dashboard reporting obligations.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>This policy establishes the continuous monitoring requirements for all organizational information systems. It defines the frequency, scope, and response procedures for ongoing security assessments, vulnerability scanning, log analysis, and security metrics reporting. Continuous monitoring supports ongoing authorization and provides the ISSM and AO with near-real-time visibility into the security posture of organizational systems. This policy implements NIST SP 800-137 Information Security Continuous Monitoring guidance. For current CDM program requirements applicable to federal agencies, see CISA Continuous Diagnostics and Mitigation program.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational information systems operating under an Authority to Operate (ATO). It applies to system owners, ISSOs, the Security Operations Center, and all personnel with monitoring or logging responsibilities. Cloud service providers handling organizational data are subject to the monitoring requirements defined in their FedRAMP authorization boundaries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Continuous_Monitoring_Policy_POL-MON-2026-005.docx</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Section 4 - Log Management Controls</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MON02.002</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>MON02.002 - Log Retention Requirements</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Static, point-in-time security assessments are insufficient for federal systems operating in a dynamic threat environment. The intent of this policy is to establish monitoring as a continuous operational function that supports timely detection of threats, configuration drift, and compliance deviations. Monitoring data shall directly inform risk register updates per the Risk Management Policy (POL-RM-2026-009), Control RMP02.001. This policy supports FISMA continuous monitoring requirements, OMB M-22-09 Zero Trust visibility requirements, and CDM program dashboard reporting obligations.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>This policy establishes the continuous monitoring requirements for all organizational information systems. It defines the frequency, scope, and response procedures for ongoing security assessments, vulnerability scanning, log analysis, and security metrics reporting. Continuous monitoring supports ongoing authorization and provides the ISSM and AO with near-real-time visibility into the security posture of organizational systems. This policy implements NIST SP 800-137 Information Security Continuous Monitoring guidance. For current CDM program requirements applicable to federal agencies, see CISA Continuous Diagnostics and Mitigation program.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational information systems operating under an Authority to Operate (ATO). It applies to system owners, ISSOs, the Security Operations Center, and all personnel with monitoring or logging responsibilities. Cloud service providers handling organizational data are subject to the monitoring requirements defined in their FedRAMP authorization boundaries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Continuous_Monitoring_Policy_POL-MON-2026-005.docx</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Section 4 - Log Management Controls</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CFG02.001</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Requirement: Security logs shall be retained for a minimum of 12 months online (immediately accessible) and 36 months total (per the Records Retention Policy and NIST AU-11 requirements). CUI-system logs require the full 36-month accessible retention with no offline-only period permitted. Log storage capacity shall be reviewed quarterly. Storage approaching 80% capacity shall trigger an immediate expansion request per the Change Management process in CFG02.001. NIST Mapping: AU-11 Status: Implemented Owner: SOC / IT Operations</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Static, point-in-time security assessments are insufficient for federal systems operating in a dynamic threat environment. The intent of this policy is to establish monitoring as a continuous operational function that supports timely detection of threats, configuration drift, and compliance deviations. Monitoring data shall directly inform risk register updates per the Risk Management Policy (POL-RM-2026-009), Control RMP02.001. This policy supports FISMA continuous monitoring requirements, OMB M-22-09 Zero Trust visibility requirements, and CDM program dashboard reporting obligations.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>This policy establishes the continuous monitoring requirements for all organizational information systems. It defines the frequency, scope, and response procedures for ongoing security assessments, vulnerability scanning, log analysis, and security metrics reporting. Continuous monitoring supports ongoing authorization and provides the ISSM and AO with near-real-time visibility into the security posture of organizational systems. This policy implements NIST SP 800-137 Information Security Continuous Monitoring guidance. For current CDM program requirements applicable to federal agencies, see CISA Continuous Diagnostics and Mitigation program.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational information systems operating under an Authority to Operate (ATO). It applies to system owners, ISSOs, the Security Operations Center, and all personnel with monitoring or logging responsibilities. Cloud service providers handling organizational data are subject to the monitoring requirements defined in their FedRAMP authorization boundaries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Continuous_Monitoring_Policy_POL-MON-2026-005.docx</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Enforcement</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>RMP03.001</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Monitoring control gaps discovered during independent assessments or audits shall result in POA&amp;M entries per RMP03.001. System owners who fail to maintain SIEM log integration or who disable monitoring tools are subject to immediate ATO suspension pending investigation. For escalation procedures, refer to the Incident Response Policy (POL-IR-2026-003). For CDM program policy updates and agency reporting requirements, see CISA CDM Program resources.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Static, point-in-time security assessments are insufficient for federal systems operating in a dynamic threat environment. The intent of this policy is to establish monitoring as a continuous operational function that supports timely detection of threats, configuration drift, and compliance deviations. Monitoring data shall directly inform risk register updates per the Risk Management Policy (POL-RM-2026-009), Control RMP02.001. This policy supports FISMA continuous monitoring requirements, OMB M-22-09 Zero Trust visibility requirements, and CDM program dashboard reporting obligations.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>This policy establishes the continuous monitoring requirements for all organizational information systems. It defines the frequency, scope, and response procedures for ongoing security assessments, vulnerability scanning, log analysis, and security metrics reporting. Continuous monitoring supports ongoing authorization and provides the ISSM and AO with near-real-time visibility into the security posture of organizational systems. This policy implements NIST SP 800-137 Information Security Continuous Monitoring guidance. For current CDM program requirements applicable to federal agencies, see CISA Continuous Diagnostics and Mitigation program.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational information systems operating under an Authority to Operate (ATO). It applies to system owners, ISSOs, the Security Operations Center, and all personnel with monitoring or logging responsibilities. Cloud service providers handling organizational data are subject to the monitoring requirements defined in their FedRAMP authorization boundaries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Continuous_Monitoring_Policy_POL-MON-2026-005.docx</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Appendix A - Vulnerability Severity Matrix and Remediation Guidance</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>MON01.002</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>This appendix supplements MON01.002 with detailed remediation guidance and two additional controls that apply to internet-facing systems with elevated risk profiles.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Static, point-in-time security assessments are insufficient for federal systems operating in a dynamic threat environment. The intent of this policy is to establish monitoring as a continuous operational function that supports timely detection of threats, configuration drift, and compliance deviations. Monitoring data shall directly inform risk register updates per the Risk Management Policy (POL-RM-2026-009), Control RMP02.001. This policy supports FISMA continuous monitoring requirements, OMB M-22-09 Zero Trust visibility requirements, and CDM program dashboard reporting obligations.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>This policy establishes the continuous monitoring requirements for all organizational information systems. It defines the frequency, scope, and response procedures for ongoing security assessments, vulnerability scanning, log analysis, and security metrics reporting. Continuous monitoring supports ongoing authorization and provides the ISSM and AO with near-real-time visibility into the security posture of organizational systems. This policy implements NIST SP 800-137 Information Security Continuous Monitoring guidance. For current CDM program requirements applicable to federal agencies, see CISA Continuous Diagnostics and Mitigation program.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational information systems operating under an Authority to Operate (ATO). It applies to system owners, ISSOs, the Security Operations Center, and all personnel with monitoring or logging responsibilities. Cloud service providers handling organizational data are subject to the monitoring requirements defined in their FedRAMP authorization boundaries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Continuous_Monitoring_Policy_POL-MON-2026-005.docx</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Appendix C - Required Log Sources</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CFG02.001</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>All sources below shall forward logs to the SIEM. The Security Engineering team maintains the SIEM integration runbook. For onboarding new log sources, submit a change request per CFG02.001. Active Directory / Entra ID - Authentication events, privilege changes, account lifecycle Windows Security Event Log - Logon/logoff, process creation, policy changes Network Firewall and IDS/IPS - Allow/deny decisions, intrusion signatures triggered VPN Gateway - Session establishment, authentication failures, data volume anomalies Email Gateway - Inbound/outbound filtering decisions, DLP policy matches Cloud Platform Audit Logs - Admin activity, data access, resource configuration changes Endpoint Detection and Response (EDR) - Process telemetry, alert events</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Static, point-in-time security assessments are insufficient for federal systems operating in a dynamic threat environment. The intent of this policy is to establish monitoring as a continuous operational function that supports timely detection of threats, configuration drift, and compliance deviations. Monitoring data shall directly inform risk register updates per the Risk Management Policy (POL-RM-2026-009), Control RMP02.001. This policy supports FISMA continuous monitoring requirements, OMB M-22-09 Zero Trust visibility requirements, and CDM program dashboard reporting obligations.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>This policy establishes the continuous monitoring requirements for all organizational information systems. It defines the frequency, scope, and response procedures for ongoing security assessments, vulnerability scanning, log analysis, and security metrics reporting. Continuous monitoring supports ongoing authorization and provides the ISSM and AO with near-real-time visibility into the security posture of organizational systems. This policy implements NIST SP 800-137 Information Security Continuous Monitoring guidance. For current CDM program requirements applicable to federal agencies, see CISA Continuous Diagnostics and Mitigation program.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational information systems operating under an Authority to Operate (ATO). It applies to system owners, ISSOs, the Security Operations Center, and all personnel with monitoring or logging responsibilities. Cloud service providers handling organizational data are subject to the monitoring requirements defined in their FedRAMP authorization boundaries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Continuous_Monitoring_Policy_POL-MON-2026-005.docx</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Appendix E - Revision History</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MON03.001</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>MON03.001 FISMA Metrics Collection The ISSO shall collect and report the six FISMA CIO metrics monthly: vulnerability management, identity management, data protection, network security, secure software lifecycle, and configuration management. Metric definitions and data sources are documented in Appendix D. PM-6 Implemented ISSO</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Static, point-in-time security assessments are insufficient for federal systems operating in a dynamic threat environment. The intent of this policy is to establish monitoring as a continuous operational function that supports timely detection of threats, configuration drift, and compliance deviations. Monitoring data shall directly inform risk register updates per the Risk Management Policy (POL-RM-2026-009), Control RMP02.001. This policy supports FISMA continuous monitoring requirements, OMB M-22-09 Zero Trust visibility requirements, and CDM program dashboard reporting obligations.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>This policy establishes the continuous monitoring requirements for all organizational information systems. It defines the frequency, scope, and response procedures for ongoing security assessments, vulnerability scanning, log analysis, and security metrics reporting. Continuous monitoring supports ongoing authorization and provides the ISSM and AO with near-real-time visibility into the security posture of organizational systems. This policy implements NIST SP 800-137 Information Security Continuous Monitoring guidance. For current CDM program requirements applicable to federal agencies, see CISA Continuous Diagnostics and Mitigation program.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational information systems operating under an Authority to Operate (ATO). It applies to system owners, ISSOs, the Security Operations Center, and all personnel with monitoring or logging responsibilities. Cloud service providers handling organizational data are subject to the monitoring requirements defined in their FedRAMP authorization boundaries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Continuous_Monitoring_Policy_POL-MON-2026-005.docx</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Appendix E - Revision History</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MON03.002</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>MON03.002 ATO Status Reporting System owners shall provide ATO status updates to the CISO quarterly. Updates shall include current POA&amp;M count by severity, upcoming reauthorization dates, and any changes to the authorization boundary. The CISO brief template is in Appendix D, Section 3. CA-7 Implemented System Owners</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Static, point-in-time security assessments are insufficient for federal systems operating in a dynamic threat environment. The intent of this policy is to establish monitoring as a continuous operational function that supports timely detection of threats, configuration drift, and compliance deviations. Monitoring data shall directly inform risk register updates per the Risk Management Policy (POL-RM-2026-009), Control RMP02.001. This policy supports FISMA continuous monitoring requirements, OMB M-22-09 Zero Trust visibility requirements, and CDM program dashboard reporting obligations.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>This policy establishes the continuous monitoring requirements for all organizational information systems. It defines the frequency, scope, and response procedures for ongoing security assessments, vulnerability scanning, log analysis, and security metrics reporting. Continuous monitoring supports ongoing authorization and provides the ISSM and AO with near-real-time visibility into the security posture of organizational systems. This policy implements NIST SP 800-137 Information Security Continuous Monitoring guidance. For current CDM program requirements applicable to federal agencies, see CISA Continuous Diagnostics and Mitigation program.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational information systems operating under an Authority to Operate (ATO). It applies to system owners, ISSOs, the Security Operations Center, and all personnel with monitoring or logging responsibilities. Cloud service providers handling organizational data are subject to the monitoring requirements defined in their FedRAMP authorization boundaries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Continuous_Monitoring_Policy_POL-MON-2026-005.docx</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Appendix E - Revision History</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MON04.001</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>MON04.001 CDM Dashboard Integration Systems covered by the CDM program shall have hardware, software, and vulnerability data integrated with the CDM agency dashboard. CDM data feeds shall be validated weekly by the Security Engineering team. Gaps in CDM data completeness shall be reported to CISA per agency CDM program requirements. PM-6, CM-8 Partially Implemented Security Engineering</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Static, point-in-time security assessments are insufficient for federal systems operating in a dynamic threat environment. The intent of this policy is to establish monitoring as a continuous operational function that supports timely detection of threats, configuration drift, and compliance deviations. Monitoring data shall directly inform risk register updates per the Risk Management Policy (POL-RM-2026-009), Control RMP02.001. This policy supports FISMA continuous monitoring requirements, OMB M-22-09 Zero Trust visibility requirements, and CDM program dashboard reporting obligations.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>This policy establishes the continuous monitoring requirements for all organizational information systems. It defines the frequency, scope, and response procedures for ongoing security assessments, vulnerability scanning, log analysis, and security metrics reporting. Continuous monitoring supports ongoing authorization and provides the ISSM and AO with near-real-time visibility into the security posture of organizational systems. This policy implements NIST SP 800-137 Information Security Continuous Monitoring guidance. For current CDM program requirements applicable to federal agencies, see CISA Continuous Diagnostics and Mitigation program.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational information systems operating under an Authority to Operate (ATO). It applies to system owners, ISSOs, the Security Operations Center, and all personnel with monitoring or logging responsibilities. Cloud service providers handling organizational data are subject to the monitoring requirements defined in their FedRAMP authorization boundaries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Continuous_Monitoring_Policy_POL-MON-2026-005.docx</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Appendix E - Revision History</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>MON04.002</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>MON04.002 Security Metrics Trending The ISSO shall produce a monthly trend report comparing current metrics to the prior 3-month baseline. Reports shall identify degrading metrics and proposed corrective actions. Reports shall be retained in SharePoint under the Monitoring Records folder per the document retention schedule in Appendix D, Section 4. PM-6 Implemented ISSO Control ID Title Requirement NIST Status Owner</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Static, point-in-time security assessments are insufficient for federal systems operating in a dynamic threat environment. The intent of this policy is to establish monitoring as a continuous operational function that supports timely detection of threats, configuration drift, and compliance deviations. Monitoring data shall directly inform risk register updates per the Risk Management Policy (POL-RM-2026-009), Control RMP02.001. This policy supports FISMA continuous monitoring requirements, OMB M-22-09 Zero Trust visibility requirements, and CDM program dashboard reporting obligations.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>This policy establishes the continuous monitoring requirements for all organizational information systems. It defines the frequency, scope, and response procedures for ongoing security assessments, vulnerability scanning, log analysis, and security metrics reporting. Continuous monitoring supports ongoing authorization and provides the ISSM and AO with near-real-time visibility into the security posture of organizational systems. This policy implements NIST SP 800-137 Information Security Continuous Monitoring guidance. For current CDM program requirements applicable to federal agencies, see CISA Continuous Diagnostics and Mitigation program.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational information systems operating under an Authority to Operate (ATO). It applies to system owners, ISSOs, the Security Operations Center, and all personnel with monitoring or logging responsibilities. Cloud service providers handling organizational data are subject to the monitoring requirements defined in their FedRAMP authorization boundaries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Continuous_Monitoring_Policy_POL-MON-2026-005.docx</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Appendix E - Revision History</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MON05.001</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>MON05.001 Continuous External Attack Surface Monitoring Internet-facing systems shall be enrolled in an automated attack surface monitoring service that performs daily external enumeration. Newly discovered assets or open ports not in the approved inventory shall generate a P2 alert. Tool and integration requirements are maintained by the Security Engineering team. RA-5(11) Partially Implemented Security Engineering</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Static, point-in-time security assessments are insufficient for federal systems operating in a dynamic threat environment. The intent of this policy is to establish monitoring as a continuous operational function that supports timely detection of threats, configuration drift, and compliance deviations. Monitoring data shall directly inform risk register updates per the Risk Management Policy (POL-RM-2026-009), Control RMP02.001. This policy supports FISMA continuous monitoring requirements, OMB M-22-09 Zero Trust visibility requirements, and CDM program dashboard reporting obligations.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>This policy establishes the continuous monitoring requirements for all organizational information systems. It defines the frequency, scope, and response procedures for ongoing security assessments, vulnerability scanning, log analysis, and security metrics reporting. Continuous monitoring supports ongoing authorization and provides the ISSM and AO with near-real-time visibility into the security posture of organizational systems. This policy implements NIST SP 800-137 Information Security Continuous Monitoring guidance. For current CDM program requirements applicable to federal agencies, see CISA Continuous Diagnostics and Mitigation program.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational information systems operating under an Authority to Operate (ATO). It applies to system owners, ISSOs, the Security Operations Center, and all personnel with monitoring or logging responsibilities. Cloud service providers handling organizational data are subject to the monitoring requirements defined in their FedRAMP authorization boundaries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Continuous_Monitoring_Policy_POL-MON-2026-005.docx</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Appendix E - Revision History</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>MON05.002</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>MON05.002 Penetration Testing Frequency</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Static, point-in-time security assessments are insufficient for federal systems operating in a dynamic threat environment. The intent of this policy is to establish monitoring as a continuous operational function that supports timely detection of threats, configuration drift, and compliance deviations. Monitoring data shall directly inform risk register updates per the Risk Management Policy (POL-RM-2026-009), Control RMP02.001. This policy supports FISMA continuous monitoring requirements, OMB M-22-09 Zero Trust visibility requirements, and CDM program dashboard reporting obligations.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>This policy establishes the continuous monitoring requirements for all organizational information systems. It defines the frequency, scope, and response procedures for ongoing security assessments, vulnerability scanning, log analysis, and security metrics reporting. Continuous monitoring supports ongoing authorization and provides the ISSM and AO with near-real-time visibility into the security posture of organizational systems. This policy implements NIST SP 800-137 Information Security Continuous Monitoring guidance. For current CDM program requirements applicable to federal agencies, see CISA Continuous Diagnostics and Mitigation program.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational information systems operating under an Authority to Operate (ATO). It applies to system owners, ISSOs, the Security Operations Center, and all personnel with monitoring or logging responsibilities. Cloud service providers handling organizational data are subject to the monitoring requirements defined in their FedRAMP authorization boundaries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Continuous_Monitoring_Policy_POL-MON-2026-005.docx</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Appendix E - Revision History</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>RMP03.001</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Internet-facing systems shall undergo penetration testing annually at minimum by a qualified independent tester. Web application penetration testing shall use OWASP methodology. Findings shall be entered as POA&amp;M items within 5 business days per RMP03.001. Pentest reports shall be retained for 3 years. CA-8 Implemented ISSO Tool Coverage Scan Type Owner Tenable Nessus / Security Center Endpoints, servers, network devices Authenticated, credentialed Security Ops Microsoft Defender Vulnerability Mgmt Windows endpoints, M365 services Agent-based continuous Endpoint Management Qualys VMDR Cloud workloads, web apps Authenticated + external Security Engineering OWASP ZAP / Burp Suite Enterprise Web applications Active DAST scanning Security Engineering Version Date Author Changes 1.4 02/01/2026 T. Okonkwo, ISSO</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Static, point-in-time security assessments are insufficient for federal systems operating in a dynamic threat environment. The intent of this policy is to establish monitoring as a continuous operational function that supports timely detection of threats, configuration drift, and compliance deviations. Monitoring data shall directly inform risk register updates per the Risk Management Policy (POL-RM-2026-009), Control RMP02.001. This policy supports FISMA continuous monitoring requirements, OMB M-22-09 Zero Trust visibility requirements, and CDM program dashboard reporting obligations.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>This policy establishes the continuous monitoring requirements for all organizational information systems. It defines the frequency, scope, and response procedures for ongoing security assessments, vulnerability scanning, log analysis, and security metrics reporting. Continuous monitoring supports ongoing authorization and provides the ISSM and AO with near-real-time visibility into the security posture of organizational systems. This policy implements NIST SP 800-137 Information Security Continuous Monitoring guidance. For current CDM program requirements applicable to federal agencies, see CISA Continuous Diagnostics and Mitigation program.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational information systems operating under an Authority to Operate (ATO). It applies to system owners, ISSOs, the Security Operations Center, and all personnel with monitoring or logging responsibilities. Cloud service providers handling organizational data are subject to the monitoring requirements defined in their FedRAMP authorization boundaries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Continuous_Monitoring_Policy_POL-MON-2026-005.docx</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Appendix E - Revision History</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>MON04.001</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Added CDM dashboard controls (MON04.001). Updated SIEM retention to 36-month. 1.3 08/15/2025 T. Okonkwo, ISSO</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Static, point-in-time security assessments are insufficient for federal systems operating in a dynamic threat environment. The intent of this policy is to establish monitoring as a continuous operational function that supports timely detection of threats, configuration drift, and compliance deviations. Monitoring data shall directly inform risk register updates per the Risk Management Policy (POL-RM-2026-009), Control RMP02.001. This policy supports FISMA continuous monitoring requirements, OMB M-22-09 Zero Trust visibility requirements, and CDM program dashboard reporting obligations.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>This policy establishes the continuous monitoring requirements for all organizational information systems. It defines the frequency, scope, and response procedures for ongoing security assessments, vulnerability scanning, log analysis, and security metrics reporting. Continuous monitoring supports ongoing authorization and provides the ISSM and AO with near-real-time visibility into the security posture of organizational systems. This policy implements NIST SP 800-137 Information Security Continuous Monitoring guidance. For current CDM program requirements applicable to federal agencies, see CISA Continuous Diagnostics and Mitigation program.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational information systems operating under an Authority to Operate (ATO). It applies to system owners, ISSOs, the Security Operations Center, and all personnel with monitoring or logging responsibilities. Cloud service providers handling organizational data are subject to the monitoring requirements defined in their FedRAMP authorization boundaries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Continuous_Monitoring_Policy_POL-MON-2026-005.docx</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Appendix E - Revision History</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>MON05.001</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Added attack surface monitoring (MON05.001). Aligned to NIST SP 800-137A. 1.2 03/01/2025 M. Johnson</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Static, point-in-time security assessments are insufficient for federal systems operating in a dynamic threat environment. The intent of this policy is to establish monitoring as a continuous operational function that supports timely detection of threats, configuration drift, and compliance deviations. Monitoring data shall directly inform risk register updates per the Risk Management Policy (POL-RM-2026-009), Control RMP02.001. This policy supports FISMA continuous monitoring requirements, OMB M-22-09 Zero Trust visibility requirements, and CDM program dashboard reporting obligations.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>This policy establishes the continuous monitoring requirements for all organizational information systems. It defines the frequency, scope, and response procedures for ongoing security assessments, vulnerability scanning, log analysis, and security metrics reporting. Continuous monitoring supports ongoing authorization and provides the ISSM and AO with near-real-time visibility into the security posture of organizational systems. This policy implements NIST SP 800-137 Information Security Continuous Monitoring guidance. For current CDM program requirements applicable to federal agencies, see CISA Continuous Diagnostics and Mitigation program.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational information systems operating under an Authority to Operate (ATO). It applies to system owners, ISSOs, the Security Operations Center, and all personnel with monitoring or logging responsibilities. Cloud service providers handling organizational data are subject to the monitoring requirements defined in their FedRAMP authorization boundaries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Continuous_Monitoring_Policy_POL-MON-2026-005.docx</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Appendix E - Revision History</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>MON05.002</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Added penetration testing control (MON05.002). Updated CVSS thresholds. 1.1 01/20/2025 M. Johnson Initial operational release post-ATO.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Static, point-in-time security assessments are insufficient for federal systems operating in a dynamic threat environment. The intent of this policy is to establish monitoring as a continuous operational function that supports timely detection of threats, configuration drift, and compliance deviations. Monitoring data shall directly inform risk register updates per the Risk Management Policy (POL-RM-2026-009), Control RMP02.001. This policy supports FISMA continuous monitoring requirements, OMB M-22-09 Zero Trust visibility requirements, and CDM program dashboard reporting obligations.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>This policy establishes the continuous monitoring requirements for all organizational information systems. It defines the frequency, scope, and response procedures for ongoing security assessments, vulnerability scanning, log analysis, and security metrics reporting. Continuous monitoring supports ongoing authorization and provides the ISSM and AO with near-real-time visibility into the security posture of organizational systems. This policy implements NIST SP 800-137 Information Security Continuous Monitoring guidance. For current CDM program requirements applicable to federal agencies, see CISA Continuous Diagnostics and Mitigation program.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational information systems operating under an Authority to Operate (ATO). It applies to system owners, ISSOs, the Security Operations Center, and all personnel with monitoring or logging responsibilities. Cloud service providers handling organizational data are subject to the monitoring requirements defined in their FedRAMP authorization boundaries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Data_Loss_Prevention_Standard_STD-DLP-2026-011.docx</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Controls</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>DLP03.002</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Controls are organized by function. For DLP alert response procedures, see DLP03.002 and Appendix E. For the approved DLP tool inventory, see Appendix A.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>This standard defines the technical and procedural requirements for preventing unauthorized disclosure of controlled unclassified information (CUI) and personally identifiable information (PII). It supplements the Information Security Program Charter and provides implementation guidance for DLP tooling and data handling controls. For federal data categorization requirements, refer to NIST SP 800-60 data categorization guidance.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>This standard applies to all systems, applications, and data flows that process, transmit, or store CUI or PII. It applies to all personnel including employees, contractors, and third-party service providers. For cloud application scope boundaries, see the Cloud Security Policy. This standard does not replace the Data Classification Policy or the Privacy Impact Assessment procedures. For data classification requirements, refer to NIST CUI Registry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Data_Loss_Prevention_Standard_STD-DLP-2026-011.docx</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Enforcement</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>IRP03.001</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>For external reporting obligations following a confirmed data loss event, refer to the Incident Response Policy (POL-IR-2026-003), Section IRP03.001.</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>This standard defines the technical and procedural requirements for preventing unauthorized disclosure of controlled unclassified information (CUI) and personally identifiable information (PII). It supplements the Information Security Program Charter and provides implementation guidance for DLP tooling and data handling controls. For federal data categorization requirements, refer to NIST SP 800-60 data categorization guidance.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>This standard applies to all systems, applications, and data flows that process, transmit, or store CUI or PII. It applies to all personnel including employees, contractors, and third-party service providers. For cloud application scope boundaries, see the Cloud Security Policy. This standard does not replace the Data Classification Policy or the Privacy Impact Assessment procedures. For data classification requirements, refer to NIST CUI Registry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Data_Loss_Prevention_Standard_STD-DLP-2026-011.docx</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Appendix B - Email Content Inspection Rules</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CFG02.001</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>For rule modification requests, submit a change request per the Configuration Management Policy (POL-CM-2026-004), Control CFG02.001.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>This standard defines the technical and procedural requirements for preventing unauthorized disclosure of controlled unclassified information (CUI) and personally identifiable information (PII). It supplements the Information Security Program Charter and provides implementation guidance for DLP tooling and data handling controls. For federal data categorization requirements, refer to NIST SP 800-60 data categorization guidance.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>This standard applies to all systems, applications, and data flows that process, transmit, or store CUI or PII. It applies to all personnel including employees, contractors, and third-party service providers. For cloud application scope boundaries, see the Cloud Security Policy. This standard does not replace the Data Classification Policy or the Privacy Impact Assessment procedures. For data classification requirements, refer to NIST CUI Registry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Data_Loss_Prevention_Standard_STD-DLP-2026-011.docx</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Appendix E - DLP Alert Triage Procedures</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>IRP01.002</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SOC personnel shall follow this triage sequence for DLP alerts: (1) Classify alert severity per the matrix in IRP02.001. (2) Identify the triggering user and data. (3) Determine if data movement was authorized. (4) If unauthorized: contain immediately, preserve logs, escalate to IR team per IRP01.002. (5) Document in case management system within 1 hour.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>This standard defines the technical and procedural requirements for preventing unauthorized disclosure of controlled unclassified information (CUI) and personally identifiable information (PII). It supplements the Information Security Program Charter and provides implementation guidance for DLP tooling and data handling controls. For federal data categorization requirements, refer to NIST SP 800-60 data categorization guidance.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>This standard applies to all systems, applications, and data flows that process, transmit, or store CUI or PII. It applies to all personnel including employees, contractors, and third-party service providers. For cloud application scope boundaries, see the Cloud Security Policy. This standard does not replace the Data Classification Policy or the Privacy Impact Assessment procedures. For data classification requirements, refer to NIST CUI Registry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Data_Loss_Prevention_Standard_STD-DLP-2026-011.docx</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Appendix E - DLP Alert Triage Procedures</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>IRP02.001</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>SOC personnel shall follow this triage sequence for DLP alerts: (1) Classify alert severity per the matrix in IRP02.001. (2) Identify the triggering user and data. (3) Determine if data movement was authorized. (4) If unauthorized: contain immediately, preserve logs, escalate to IR team per IRP01.002. (5) Document in case management system within 1 hour.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>This standard defines the technical and procedural requirements for preventing unauthorized disclosure of controlled unclassified information (CUI) and personally identifiable information (PII). It supplements the Information Security Program Charter and provides implementation guidance for DLP tooling and data handling controls. For federal data categorization requirements, refer to NIST SP 800-60 data categorization guidance.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>This standard applies to all systems, applications, and data flows that process, transmit, or store CUI or PII. It applies to all personnel including employees, contractors, and third-party service providers. For cloud application scope boundaries, see the Cloud Security Policy. This standard does not replace the Data Classification Policy or the Privacy Impact Assessment procedures. For data classification requirements, refer to NIST CUI Registry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Data_Loss_Prevention_Standard_STD-DLP-2026-011.docx</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>DLP01.001</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>DLP01.001 DLP Tool Deployment The organization shall deploy DLP tooling on all endpoints and email gateways to inspect outbound data flows for CUI and PII. See Appendix A for approved DLP tool list. SI-12 Implemented Security Ops</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>This standard defines the technical and procedural requirements for preventing unauthorized disclosure of controlled unclassified information (CUI) and personally identifiable information (PII). It supplements the Information Security Program Charter and provides implementation guidance for DLP tooling and data handling controls. For federal data categorization requirements, refer to NIST SP 800-60 data categorization guidance.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>This standard applies to all systems, applications, and data flows that process, transmit, or store CUI or PII. It applies to all personnel including employees, contractors, and third-party service providers. For cloud application scope boundaries, see the Cloud Security Policy. This standard does not replace the Data Classification Policy or the Privacy Impact Assessment procedures. For data classification requirements, refer to NIST CUI Registry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Data_Loss_Prevention_Standard_STD-DLP-2026-011.docx</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>DLP01.002</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>DLP01.002 Content Inspection Policy Outbound email shall be subject to automated content inspection as described in Section 2 of this standard. Policy rules are documented in Appendix B. SI-12 Implemented Security Ops</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>This standard defines the technical and procedural requirements for preventing unauthorized disclosure of controlled unclassified information (CUI) and personally identifiable information (PII). It supplements the Information Security Program Charter and provides implementation guidance for DLP tooling and data handling controls. For federal data categorization requirements, refer to NIST SP 800-60 data categorization guidance.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>This standard applies to all systems, applications, and data flows that process, transmit, or store CUI or PII. It applies to all personnel including employees, contractors, and third-party service providers. For cloud application scope boundaries, see the Cloud Security Policy. This standard does not replace the Data Classification Policy or the Privacy Impact Assessment procedures. For data classification requirements, refer to NIST CUI Registry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Data_Loss_Prevention_Standard_STD-DLP-2026-011.docx</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>DLP02.001</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>DLP02.001 Data Classification Tagging All documents containing CUI shall be tagged with approved sensitivity labels per the Data Classification Policy. See Appendix C for label taxonomy. MP-3 Implemented All Users</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>This standard defines the technical and procedural requirements for preventing unauthorized disclosure of controlled unclassified information (CUI) and personally identifiable information (PII). It supplements the Information Security Program Charter and provides implementation guidance for DLP tooling and data handling controls. For federal data categorization requirements, refer to NIST SP 800-60 data categorization guidance.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>This standard applies to all systems, applications, and data flows that process, transmit, or store CUI or PII. It applies to all personnel including employees, contractors, and third-party service providers. For cloud application scope boundaries, see the Cloud Security Policy. This standard does not replace the Data Classification Policy or the Privacy Impact Assessment procedures. For data classification requirements, refer to NIST CUI Registry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Data_Loss_Prevention_Standard_STD-DLP-2026-011.docx</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>DLP02.002</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>DLP02.002 Endpoint DLP Enforcement DLP agents on endpoints shall enforce block actions for attempted exfiltration of CUI to unapproved destinations. Exceptions require ISSM approval per Appendix D. SI-3 Partially Implemented Endpoint Mgmt</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>This standard defines the technical and procedural requirements for preventing unauthorized disclosure of controlled unclassified information (CUI) and personally identifiable information (PII). It supplements the Information Security Program Charter and provides implementation guidance for DLP tooling and data handling controls. For federal data categorization requirements, refer to NIST SP 800-60 data categorization guidance.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>This standard applies to all systems, applications, and data flows that process, transmit, or store CUI or PII. It applies to all personnel including employees, contractors, and third-party service providers. For cloud application scope boundaries, see the Cloud Security Policy. This standard does not replace the Data Classification Policy or the Privacy Impact Assessment procedures. For data classification requirements, refer to NIST CUI Registry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Data_Loss_Prevention_Standard_STD-DLP-2026-011.docx</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>DLP03.001</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>DLP03.001 Cloud Application Controls Sanctioned cloud applications shall be configured with DLP policies restricting upload of sensitive data. Unsanctioned apps shall be blocked per the Network Security Policy. SC-7 Implemented Cloud Security</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>This standard defines the technical and procedural requirements for preventing unauthorized disclosure of controlled unclassified information (CUI) and personally identifiable information (PII). It supplements the Information Security Program Charter and provides implementation guidance for DLP tooling and data handling controls. For federal data categorization requirements, refer to NIST SP 800-60 data categorization guidance.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>This standard applies to all systems, applications, and data flows that process, transmit, or store CUI or PII. It applies to all personnel including employees, contractors, and third-party service providers. For cloud application scope boundaries, see the Cloud Security Policy. This standard does not replace the Data Classification Policy or the Privacy Impact Assessment procedures. For data classification requirements, refer to NIST CUI Registry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Data_Loss_Prevention_Standard_STD-DLP-2026-011.docx</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>DLP03.002</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DLP03.002 DLP Alert Response SLA DLP alerts classified as High or Critical shall be investigated within 2 hours by the SOC. Alert triage procedures are in Appendix E. IR-5 Implemented SOC</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>This standard defines the technical and procedural requirements for preventing unauthorized disclosure of controlled unclassified information (CUI) and personally identifiable information (PII). It supplements the Information Security Program Charter and provides implementation guidance for DLP tooling and data handling controls. For federal data categorization requirements, refer to NIST SP 800-60 data categorization guidance.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>This standard applies to all systems, applications, and data flows that process, transmit, or store CUI or PII. It applies to all personnel including employees, contractors, and third-party service providers. For cloud application scope boundaries, see the Cloud Security Policy. This standard does not replace the Data Classification Policy or the Privacy Impact Assessment procedures. For data classification requirements, refer to NIST CUI Registry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Data_Loss_Prevention_Standard_STD-DLP-2026-011.docx</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>DLP04.001</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>DLP04.001 Removable Media Enforcement DLP tooling shall enforce encryption requirements for all data written to removable media per the Encryption Policy, Section 2.1. MP-7 Implemented Endpoint Mgmt</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>This standard defines the technical and procedural requirements for preventing unauthorized disclosure of controlled unclassified information (CUI) and personally identifiable information (PII). It supplements the Information Security Program Charter and provides implementation guidance for DLP tooling and data handling controls. For federal data categorization requirements, refer to NIST SP 800-60 data categorization guidance.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>This standard applies to all systems, applications, and data flows that process, transmit, or store CUI or PII. It applies to all personnel including employees, contractors, and third-party service providers. For cloud application scope boundaries, see the Cloud Security Policy. This standard does not replace the Data Classification Policy or the Privacy Impact Assessment procedures. For data classification requirements, refer to NIST CUI Registry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Data_Loss_Prevention_Standard_STD-DLP-2026-011.docx</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>DLP04.002</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>DLP04.002 Print and Fax Controls Printing of CUI documents shall be logged. Fax transmission of CUI is prohibited unless using an approved secure fax solution per Appendix F. MP-2 Not Implemented Facilities Tool Coverage Owner Review Date Microsoft Purview DLP Email, SharePoint, OneDrive, Endpoints Security Ops Quarterly Defender for Endpoint Endpoint file operations, USB Endpoint Mgmt Quarterly Network DLP (Proxy) Web uploads, cloud app traffic Network Ops Semi-annual Label Category Handling Requirement UNCLASSIFIED Public / Internal No restrictions beyond standard acceptable use. CUI Controlled Unclassified Encrypt at rest and in transit. Restrict sharing to need-to-know. CUI//SP-CTI Cyber Threat Intel Additional access restrictions per CUI SP handling requirements. FOUO For Official Use Only Legacy label. Map to CUI for new documents. Version Date Author Changes 1.3 03/01/2026 A. Patel, Security Ops</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>This standard defines the technical and procedural requirements for preventing unauthorized disclosure of controlled unclassified information (CUI) and personally identifiable information (PII). It supplements the Information Security Program Charter and provides implementation guidance for DLP tooling and data handling controls. For federal data categorization requirements, refer to NIST SP 800-60 data categorization guidance.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>This standard applies to all systems, applications, and data flows that process, transmit, or store CUI or PII. It applies to all personnel including employees, contractors, and third-party service providers. For cloud application scope boundaries, see the Cloud Security Policy. This standard does not replace the Data Classification Policy or the Privacy Impact Assessment procedures. For data classification requirements, refer to NIST CUI Registry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Data_Loss_Prevention_Standard_STD-DLP-2026-011.docx</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>DLP03.001</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Added cloud application controls (DLP03.001) 1.2 09/15/2025 A. Patel, Security Ops Updated Purview label taxonomy in Appendix C 1.1 03/10/2025 M. Johnson Added endpoint DLP controls, Appendix D exception process 1.0 01/15/2025 M. Johnson Initial release</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>This standard defines the technical and procedural requirements for preventing unauthorized disclosure of controlled unclassified information (CUI) and personally identifiable information (PII). It supplements the Information Security Program Charter and provides implementation guidance for DLP tooling and data handling controls. For federal data categorization requirements, refer to NIST SP 800-60 data categorization guidance.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>This standard applies to all systems, applications, and data flows that process, transmit, or store CUI or PII. It applies to all personnel including employees, contractors, and third-party service providers. For cloud application scope boundaries, see the Cloud Security Policy. This standard does not replace the Data Classification Policy or the Privacy Impact Assessment procedures. For data classification requirements, refer to NIST CUI Registry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Encryption_Policy_POL-ENC-2026-008.docx</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Section 3 - Data-at-Rest Encryption Controls</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>CFG01.001</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>The following controls govern encryption of data stored on organizational systems, endpoints, and removable media. These controls apply to all storage classes regardless of whether the system is on-premises or cloud-hosted. Non-compliance with these controls shall be treated as a configuration management deficiency per the Configuration Management Policy (POL-CM-2026-004), Control CFG01.001.</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>This policy establishes the cryptographic requirements for protecting organizational data at rest and in transit. It defines approved algorithms, key management procedures, and implementation requirements for all information systems operated by the organization. This policy implements NIST SP 800-111, NIST SP 800-52 Rev 2, and FIPS 140-3 requirements. For a plain-language overview of federal cryptographic standards, see the NIST Cryptographic Standards and Guidelines portal.</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>This policy applies to all information systems, applications, and data stores that process, transmit, or store CUI, PII, or data classified at FIPS 199 Moderate or High impact levels. It applies to all personnel with system administration, development, or data handling responsibilities. BYOD encryption requirements are addressed in conjunction with the Mobile Device Management Policy. For cloud-specific encryption inheritance, refer to the FedRAMP authorization documentation for each cloud service in use. For current FIPS 140-3 validated module listings, see the NIST Cryptographic Module Validation Program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Encryption_Policy_POL-ENC-2026-008.docx</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Section 3 - Data-at-Rest Encryption Controls</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ENC01.001</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ENC01.001 - Full Disk Encryption for Endpoints Requirement: All organizational laptops, workstations, and mobile devices shall have full disk encryption (FDE) enabled using a FIPS 140-3 validated module. BitLocker with TPM 2.0 is the approved solution for Windows endpoints. Recovery keys shall be escrowed in Active Directory or Azure AD per the key management procedures in Appendix A. Devices failing FDE compliance checks shall be quarantined from the network within 24 hours. NIST Mapping: SC-28, SC-28(1) Status: Implemented Owner: Endpoint Management</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>This policy establishes the cryptographic requirements for protecting organizational data at rest and in transit. It defines approved algorithms, key management procedures, and implementation requirements for all information systems operated by the organization. This policy implements NIST SP 800-111, NIST SP 800-52 Rev 2, and FIPS 140-3 requirements. For a plain-language overview of federal cryptographic standards, see the NIST Cryptographic Standards and Guidelines portal.</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>This policy applies to all information systems, applications, and data stores that process, transmit, or store CUI, PII, or data classified at FIPS 199 Moderate or High impact levels. It applies to all personnel with system administration, development, or data handling responsibilities. BYOD encryption requirements are addressed in conjunction with the Mobile Device Management Policy. For cloud-specific encryption inheritance, refer to the FedRAMP authorization documentation for each cloud service in use. For current FIPS 140-3 validated module listings, see the NIST Cryptographic Module Validation Program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Encryption_Policy_POL-ENC-2026-008.docx</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Section 3 - Data-at-Rest Encryption Controls</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ENC01.002</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ENC01.002 - Database Encryption</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>This policy establishes the cryptographic requirements for protecting organizational data at rest and in transit. It defines approved algorithms, key management procedures, and implementation requirements for all information systems operated by the organization. This policy implements NIST SP 800-111, NIST SP 800-52 Rev 2, and FIPS 140-3 requirements. For a plain-language overview of federal cryptographic standards, see the NIST Cryptographic Standards and Guidelines portal.</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>This policy applies to all information systems, applications, and data stores that process, transmit, or store CUI, PII, or data classified at FIPS 199 Moderate or High impact levels. It applies to all personnel with system administration, development, or data handling responsibilities. BYOD encryption requirements are addressed in conjunction with the Mobile Device Management Policy. For cloud-specific encryption inheritance, refer to the FedRAMP authorization documentation for each cloud service in use. For current FIPS 140-3 validated module listings, see the NIST Cryptographic Module Validation Program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Encryption_Policy_POL-ENC-2026-008.docx</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Section 3 - Data-at-Rest Encryption Controls</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>CFG03.001</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Requirement: All databases storing CUI or PII shall implement Transparent Data Encryption (TDE) using AES-256. Database encryption keys shall be stored in the approved key management system, not on the same server as the encrypted data. See Appendix A for key storage requirements. Database administrators shall verify TDE status quarterly and document results in the configuration compliance report per CFG03.001. NIST Mapping: SC-28 Status: Implemented Owner: Database Administration</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>This policy establishes the cryptographic requirements for protecting organizational data at rest and in transit. It defines approved algorithms, key management procedures, and implementation requirements for all information systems operated by the organization. This policy implements NIST SP 800-111, NIST SP 800-52 Rev 2, and FIPS 140-3 requirements. For a plain-language overview of federal cryptographic standards, see the NIST Cryptographic Standards and Guidelines portal.</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>This policy applies to all information systems, applications, and data stores that process, transmit, or store CUI, PII, or data classified at FIPS 199 Moderate or High impact levels. It applies to all personnel with system administration, development, or data handling responsibilities. BYOD encryption requirements are addressed in conjunction with the Mobile Device Management Policy. For cloud-specific encryption inheritance, refer to the FedRAMP authorization documentation for each cloud service in use. For current FIPS 140-3 validated module listings, see the NIST Cryptographic Module Validation Program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Encryption_Policy_POL-ENC-2026-008.docx</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Section 4 - Data-in-Transit Encryption Controls</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ENC02.001</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ENC02.001 - TLS Requirements for Web Applications Requirement: All web applications and APIs accessible internally or externally shall enforce TLS 1.2 or TLS 1.3. TLS 1.0 and TLS 1.1 are prohibited per Appendix C. Certificate management shall follow the procedures in Appendix D. Expired or self-signed certificates on production systems constitute a Level 3 policy violation per the Acceptable Use Policy, Section 6. Automated certificate monitoring shall alert the Security Operations team 30 days before expiration. NIST Mapping: SC-8, SC-8(1) Status: Implemented Owner: Security Engineering</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>This policy establishes the cryptographic requirements for protecting organizational data at rest and in transit. It defines approved algorithms, key management procedures, and implementation requirements for all information systems operated by the organization. This policy implements NIST SP 800-111, NIST SP 800-52 Rev 2, and FIPS 140-3 requirements. For a plain-language overview of federal cryptographic standards, see the NIST Cryptographic Standards and Guidelines portal.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>This policy applies to all information systems, applications, and data stores that process, transmit, or store CUI, PII, or data classified at FIPS 199 Moderate or High impact levels. It applies to all personnel with system administration, development, or data handling responsibilities. BYOD encryption requirements are addressed in conjunction with the Mobile Device Management Policy. For cloud-specific encryption inheritance, refer to the FedRAMP authorization documentation for each cloud service in use. For current FIPS 140-3 validated module listings, see the NIST Cryptographic Module Validation Program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Encryption_Policy_POL-ENC-2026-008.docx</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Section 4 - Data-in-Transit Encryption Controls</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ENC02.002</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ENC02.002 - Email Encryption for CUI Transmission</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>This policy establishes the cryptographic requirements for protecting organizational data at rest and in transit. It defines approved algorithms, key management procedures, and implementation requirements for all information systems operated by the organization. This policy implements NIST SP 800-111, NIST SP 800-52 Rev 2, and FIPS 140-3 requirements. For a plain-language overview of federal cryptographic standards, see the NIST Cryptographic Standards and Guidelines portal.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>This policy applies to all information systems, applications, and data stores that process, transmit, or store CUI, PII, or data classified at FIPS 199 Moderate or High impact levels. It applies to all personnel with system administration, development, or data handling responsibilities. BYOD encryption requirements are addressed in conjunction with the Mobile Device Management Policy. For cloud-specific encryption inheritance, refer to the FedRAMP authorization documentation for each cloud service in use. For current FIPS 140-3 validated module listings, see the NIST Cryptographic Module Validation Program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Encryption_Policy_POL-ENC-2026-008.docx</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Section 4 - Data-in-Transit Encryption Controls</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>DLP01.002</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Requirement: CUI transmitted via email shall use S/MIME or an approved secure messaging gateway. Auto-forwarding of encrypted email to external accounts is prohibited per the Acceptable Use Policy (POL-AU-2026-006). For inter-agency CUI transmission, the organization shall use approved government messaging solutions. See the DLP Standard (STD-DLP-2026-011), Control DLP01.002, for the automated content inspection requirements that enforce this control. NIST Mapping: SC-8 Status: Partially Implemented Owner: Security Engineering</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>This policy establishes the cryptographic requirements for protecting organizational data at rest and in transit. It defines approved algorithms, key management procedures, and implementation requirements for all information systems operated by the organization. This policy implements NIST SP 800-111, NIST SP 800-52 Rev 2, and FIPS 140-3 requirements. For a plain-language overview of federal cryptographic standards, see the NIST Cryptographic Standards and Guidelines portal.</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>This policy applies to all information systems, applications, and data stores that process, transmit, or store CUI, PII, or data classified at FIPS 199 Moderate or High impact levels. It applies to all personnel with system administration, development, or data handling responsibilities. BYOD encryption requirements are addressed in conjunction with the Mobile Device Management Policy. For cloud-specific encryption inheritance, refer to the FedRAMP authorization documentation for each cloud service in use. For current FIPS 140-3 validated module listings, see the NIST Cryptographic Module Validation Program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Encryption_Policy_POL-ENC-2026-008.docx</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Enforcement</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>RMP03.001</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Encryption control failures detected during configuration scanning (CFG03.001) shall generate POA&amp;M entries per the Risk Management Policy (POL-RM-2026-009), Control RMP03.001. Systems found to be out of compliance with this policy shall not be authorized to process CUI until remediation is complete and verified.</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>This policy establishes the cryptographic requirements for protecting organizational data at rest and in transit. It defines approved algorithms, key management procedures, and implementation requirements for all information systems operated by the organization. This policy implements NIST SP 800-111, NIST SP 800-52 Rev 2, and FIPS 140-3 requirements. For a plain-language overview of federal cryptographic standards, see the NIST Cryptographic Standards and Guidelines portal.</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>This policy applies to all information systems, applications, and data stores that process, transmit, or store CUI, PII, or data classified at FIPS 199 Moderate or High impact levels. It applies to all personnel with system administration, development, or data handling responsibilities. BYOD encryption requirements are addressed in conjunction with the Mobile Device Management Policy. For cloud-specific encryption inheritance, refer to the FedRAMP authorization documentation for each cloud service in use. For current FIPS 140-3 validated module listings, see the NIST Cryptographic Module Validation Program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Encryption_Policy_POL-ENC-2026-008.docx</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Enforcement</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>CFG03.001</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Encryption control failures detected during configuration scanning (CFG03.001) shall generate POA&amp;M entries per the Risk Management Policy (POL-RM-2026-009), Control RMP03.001. Systems found to be out of compliance with this policy shall not be authorized to process CUI until remediation is complete and verified. For questions about FIPS-validated module selection, see the NIST CMVP search tool. For certificate procurement procedures, contact the PKI team via the IT Service Portal.</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>This policy establishes the cryptographic requirements for protecting organizational data at rest and in transit. It defines approved algorithms, key management procedures, and implementation requirements for all information systems operated by the organization. This policy implements NIST SP 800-111, NIST SP 800-52 Rev 2, and FIPS 140-3 requirements. For a plain-language overview of federal cryptographic standards, see the NIST Cryptographic Standards and Guidelines portal.</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>This policy applies to all information systems, applications, and data stores that process, transmit, or store CUI, PII, or data classified at FIPS 199 Moderate or High impact levels. It applies to all personnel with system administration, development, or data handling responsibilities. BYOD encryption requirements are addressed in conjunction with the Mobile Device Management Policy. For cloud-specific encryption inheritance, refer to the FedRAMP authorization documentation for each cloud service in use. For current FIPS 140-3 validated module listings, see the NIST Cryptographic Module Validation Program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Encryption_Policy_POL-ENC-2026-008.docx</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Appendix A - Key Lifecycle Management Procedures</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ENC03.002</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>This appendix contains the procedural detail supporting key management controls ENC03.001, ENC03.002, ENC04.001, and ENC04.002. It also contains two additional controls governing key escrow and key ceremony requirements that apply only to systems processing data classified at FIPS High impact level.</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>This policy establishes the cryptographic requirements for protecting organizational data at rest and in transit. It defines approved algorithms, key management procedures, and implementation requirements for all information systems operated by the organization. This policy implements NIST SP 800-111, NIST SP 800-52 Rev 2, and FIPS 140-3 requirements. For a plain-language overview of federal cryptographic standards, see the NIST Cryptographic Standards and Guidelines portal.</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>This policy applies to all information systems, applications, and data stores that process, transmit, or store CUI, PII, or data classified at FIPS 199 Moderate or High impact levels. It applies to all personnel with system administration, development, or data handling responsibilities. BYOD encryption requirements are addressed in conjunction with the Mobile Device Management Policy. For cloud-specific encryption inheritance, refer to the FedRAMP authorization documentation for each cloud service in use. For current FIPS 140-3 validated module listings, see the NIST Cryptographic Module Validation Program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Encryption_Policy_POL-ENC-2026-008.docx</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Appendix A - Key Lifecycle Management Procedures</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ENC04.001</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>This appendix contains the procedural detail supporting key management controls ENC03.001, ENC03.002, ENC04.001, and ENC04.002. It also contains two additional controls governing key escrow and key ceremony requirements that apply only to systems processing data classified at FIPS High impact level.</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>This policy establishes the cryptographic requirements for protecting organizational data at rest and in transit. It defines approved algorithms, key management procedures, and implementation requirements for all information systems operated by the organization. This policy implements NIST SP 800-111, NIST SP 800-52 Rev 2, and FIPS 140-3 requirements. For a plain-language overview of federal cryptographic standards, see the NIST Cryptographic Standards and Guidelines portal.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>This policy applies to all information systems, applications, and data stores that process, transmit, or store CUI, PII, or data classified at FIPS 199 Moderate or High impact levels. It applies to all personnel with system administration, development, or data handling responsibilities. BYOD encryption requirements are addressed in conjunction with the Mobile Device Management Policy. For cloud-specific encryption inheritance, refer to the FedRAMP authorization documentation for each cloud service in use. For current FIPS 140-3 validated module listings, see the NIST Cryptographic Module Validation Program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Encryption_Policy_POL-ENC-2026-008.docx</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Appendix A - Key Lifecycle Management Procedures</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ENC04.002</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>This appendix contains the procedural detail supporting key management controls ENC03.001, ENC03.002, ENC04.001, and ENC04.002. It also contains two additional controls governing key escrow and key ceremony requirements that apply only to systems processing data classified at FIPS High impact level.</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>This policy establishes the cryptographic requirements for protecting organizational data at rest and in transit. It defines approved algorithms, key management procedures, and implementation requirements for all information systems operated by the organization. This policy implements NIST SP 800-111, NIST SP 800-52 Rev 2, and FIPS 140-3 requirements. For a plain-language overview of federal cryptographic standards, see the NIST Cryptographic Standards and Guidelines portal.</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>This policy applies to all information systems, applications, and data stores that process, transmit, or store CUI, PII, or data classified at FIPS 199 Moderate or High impact levels. It applies to all personnel with system administration, development, or data handling responsibilities. BYOD encryption requirements are addressed in conjunction with the Mobile Device Management Policy. For cloud-specific encryption inheritance, refer to the FedRAMP authorization documentation for each cloud service in use. For current FIPS 140-3 validated module listings, see the NIST Cryptographic Module Validation Program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Encryption_Policy_POL-ENC-2026-008.docx</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Appendix A - Key Lifecycle Management Procedures</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ENC03.001</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>This appendix contains the procedural detail supporting key management controls ENC03.001, ENC03.002, ENC04.001, and ENC04.002. It also contains two additional controls governing key escrow and key ceremony requirements that apply only to systems processing data classified at FIPS High impact level.</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>This policy establishes the cryptographic requirements for protecting organizational data at rest and in transit. It defines approved algorithms, key management procedures, and implementation requirements for all information systems operated by the organization. This policy implements NIST SP 800-111, NIST SP 800-52 Rev 2, and FIPS 140-3 requirements. For a plain-language overview of federal cryptographic standards, see the NIST Cryptographic Standards and Guidelines portal.</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>This policy applies to all information systems, applications, and data stores that process, transmit, or store CUI, PII, or data classified at FIPS 199 Moderate or High impact levels. It applies to all personnel with system administration, development, or data handling responsibilities. BYOD encryption requirements are addressed in conjunction with the Mobile Device Management Policy. For cloud-specific encryption inheritance, refer to the FedRAMP authorization documentation for each cloud service in use. For current FIPS 140-3 validated module listings, see the NIST Cryptographic Module Validation Program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Encryption_Policy_POL-ENC-2026-008.docx</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Appendix A Controls - High Impact Key Management</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ENC05.001</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ENC05.001 - Key Escrow for High-Impact Systems Requirement: Encryption keys protecting High-impact systems shall be escrowed with a secondary custodian independent of the primary key owner. Escrowed keys shall be stored in a separate HSM partition with dual-control access requiring two authorized custodians. Escrow access events shall be logged and reviewed by the ISSO within 24 hours. For key escrow procedures, contact the Security Engineering team. NIST Mapping: SC-12(6) Status: Implemented Owner: Security Engineering</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>This policy establishes the cryptographic requirements for protecting organizational data at rest and in transit. It defines approved algorithms, key management procedures, and implementation requirements for all information systems operated by the organization. This policy implements NIST SP 800-111, NIST SP 800-52 Rev 2, and FIPS 140-3 requirements. For a plain-language overview of federal cryptographic standards, see the NIST Cryptographic Standards and Guidelines portal.</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>This policy applies to all information systems, applications, and data stores that process, transmit, or store CUI, PII, or data classified at FIPS 199 Moderate or High impact levels. It applies to all personnel with system administration, development, or data handling responsibilities. BYOD encryption requirements are addressed in conjunction with the Mobile Device Management Policy. For cloud-specific encryption inheritance, refer to the FedRAMP authorization documentation for each cloud service in use. For current FIPS 140-3 validated module listings, see the NIST Cryptographic Module Validation Program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Encryption_Policy_POL-ENC-2026-008.docx</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Appendix A Controls - High Impact Key Management</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ENC05.002</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ENC05.002 - Key Generation Ceremony Requirements Requirement: Root CA key generation and HSM master key initialization shall follow a documented key ceremony procedure with a minimum of three witnesses, one of whom shall be the ISSM or designated representative. The ceremony shall be video recorded and the recording stored per the Records Retention Policy. Key ceremony logs shall be retained for the life of the key plus 5 years. NIST Mapping: SC-12 Status: Implemented Owner: ISSO / Security Engineering</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>This policy establishes the cryptographic requirements for protecting organizational data at rest and in transit. It defines approved algorithms, key management procedures, and implementation requirements for all information systems operated by the organization. This policy implements NIST SP 800-111, NIST SP 800-52 Rev 2, and FIPS 140-3 requirements. For a plain-language overview of federal cryptographic standards, see the NIST Cryptographic Standards and Guidelines portal.</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>This policy applies to all information systems, applications, and data stores that process, transmit, or store CUI, PII, or data classified at FIPS 199 Moderate or High impact levels. It applies to all personnel with system administration, development, or data handling responsibilities. BYOD encryption requirements are addressed in conjunction with the Mobile Device Management Policy. For cloud-specific encryption inheritance, refer to the FedRAMP authorization documentation for each cloud service in use. For current FIPS 140-3 validated module listings, see the NIST Cryptographic Module Validation Program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Encryption_Policy_POL-ENC-2026-008.docx</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Appendix E - Revision History</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ENC03.001</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ENC03.001 Key Generation Standards Cryptographic keys shall be generated using NIST SP 800-133-approved methods with a FIPS 140-3 validated RNG. Key length minimums: AES 256-bit, RSA 3072-bit, ECDSA P-384. Keys generated outside these parameters shall not be used for CUI protection. SC-12 Implemented Security Engineering</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>This policy establishes the cryptographic requirements for protecting organizational data at rest and in transit. It defines approved algorithms, key management procedures, and implementation requirements for all information systems operated by the organization. This policy implements NIST SP 800-111, NIST SP 800-52 Rev 2, and FIPS 140-3 requirements. For a plain-language overview of federal cryptographic standards, see the NIST Cryptographic Standards and Guidelines portal.</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>This policy applies to all information systems, applications, and data stores that process, transmit, or store CUI, PII, or data classified at FIPS 199 Moderate or High impact levels. It applies to all personnel with system administration, development, or data handling responsibilities. BYOD encryption requirements are addressed in conjunction with the Mobile Device Management Policy. For cloud-specific encryption inheritance, refer to the FedRAMP authorization documentation for each cloud service in use. For current FIPS 140-3 validated module listings, see the NIST Cryptographic Module Validation Program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Encryption_Policy_POL-ENC-2026-008.docx</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Appendix E - Revision History</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ENC03.002</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ENC03.002 Key Storage and Protection Private keys shall be stored in a FIPS 140-3 Level 2 or higher Hardware Security Module (HSM). Plaintext private keys shall never reside on general-purpose file systems. HSM access logs shall be reviewed monthly per Appendix A, Section 4. SC-12(1) Implemented Security Engineering</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>This policy establishes the cryptographic requirements for protecting organizational data at rest and in transit. It defines approved algorithms, key management procedures, and implementation requirements for all information systems operated by the organization. This policy implements NIST SP 800-111, NIST SP 800-52 Rev 2, and FIPS 140-3 requirements. For a plain-language overview of federal cryptographic standards, see the NIST Cryptographic Standards and Guidelines portal.</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>This policy applies to all information systems, applications, and data stores that process, transmit, or store CUI, PII, or data classified at FIPS 199 Moderate or High impact levels. It applies to all personnel with system administration, development, or data handling responsibilities. BYOD encryption requirements are addressed in conjunction with the Mobile Device Management Policy. For cloud-specific encryption inheritance, refer to the FedRAMP authorization documentation for each cloud service in use. For current FIPS 140-3 validated module listings, see the NIST Cryptographic Module Validation Program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Encryption_Policy_POL-ENC-2026-008.docx</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Appendix E - Revision History</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ENC04.001</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ENC04.001 Key Rotation Schedule Symmetric keys used for CUI encryption shall be rotated annually or immediately upon suspected compromise. TLS certificates shall be rotated annually. Key rotation events shall be logged in the key management system and reported to the ISSO within 48 hours of completion. SC-12 Implemented Security Engineering</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>This policy establishes the cryptographic requirements for protecting organizational data at rest and in transit. It defines approved algorithms, key management procedures, and implementation requirements for all information systems operated by the organization. This policy implements NIST SP 800-111, NIST SP 800-52 Rev 2, and FIPS 140-3 requirements. For a plain-language overview of federal cryptographic standards, see the NIST Cryptographic Standards and Guidelines portal.</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>This policy applies to all information systems, applications, and data stores that process, transmit, or store CUI, PII, or data classified at FIPS 199 Moderate or High impact levels. It applies to all personnel with system administration, development, or data handling responsibilities. BYOD encryption requirements are addressed in conjunction with the Mobile Device Management Policy. For cloud-specific encryption inheritance, refer to the FedRAMP authorization documentation for each cloud service in use. For current FIPS 140-3 validated module listings, see the NIST Cryptographic Module Validation Program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Encryption_Policy_POL-ENC-2026-008.docx</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Appendix E - Revision History</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ENC04.002</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ENC04.002 Key Revocation and Destruction Compromised or expired keys shall be revoked and destroyed within 4 hours of determination. Destruction shall use NIST SP 800-88 approved methods. Certificate revocation shall update the organizational CRL within 1 hour. Destruction events are documented per Appendix A, Section 5. SC-12 Implemented Security Engineering Protocol Version Use Case Notes TLS 1.2, 1.3 All web and API traffic 1.3 preferred. FIPS cipher suites only. SSH 2.0 Administrative access RSA 3072-bit or ECDSA P-384 keys only. IPSec / IKEv2 IKEv2 VPN tunnels</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>This policy establishes the cryptographic requirements for protecting organizational data at rest and in transit. It defines approved algorithms, key management procedures, and implementation requirements for all information systems operated by the organization. This policy implements NIST SP 800-111, NIST SP 800-52 Rev 2, and FIPS 140-3 requirements. For a plain-language overview of federal cryptographic standards, see the NIST Cryptographic Standards and Guidelines portal.</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>This policy applies to all information systems, applications, and data stores that process, transmit, or store CUI, PII, or data classified at FIPS 199 Moderate or High impact levels. It applies to all personnel with system administration, development, or data handling responsibilities. BYOD encryption requirements are addressed in conjunction with the Mobile Device Management Policy. For cloud-specific encryption inheritance, refer to the FedRAMP authorization documentation for each cloud service in use. For current FIPS 140-3 validated module listings, see the NIST Cryptographic Module Validation Program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Encryption_Policy_POL-ENC-2026-008.docx</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Appendix E - Revision History</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ACC02.001</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AES-256-GCM, SHA-384. See ACC02.001. S/MIME 3.2+ Email encryption</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>This policy establishes the cryptographic requirements for protecting organizational data at rest and in transit. It defines approved algorithms, key management procedures, and implementation requirements for all information systems operated by the organization. This policy implements NIST SP 800-111, NIST SP 800-52 Rev 2, and FIPS 140-3 requirements. For a plain-language overview of federal cryptographic standards, see the NIST Cryptographic Standards and Guidelines portal.</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>This policy applies to all information systems, applications, and data stores that process, transmit, or store CUI, PII, or data classified at FIPS 199 Moderate or High impact levels. It applies to all personnel with system administration, development, or data handling responsibilities. BYOD encryption requirements are addressed in conjunction with the Mobile Device Management Policy. For cloud-specific encryption inheritance, refer to the FedRAMP authorization documentation for each cloud service in use. For current FIPS 140-3 validated module listings, see the NIST Cryptographic Module Validation Program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Encryption_Policy_POL-ENC-2026-008.docx</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Appendix E - Revision History</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ENC02.002</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Required for CUI email. See ENC02.002. HTTPS via TLS 1.2+ Web applications HSTS enforced with 1-year max-age. Version Date Author Changes 2.2 01/15/2026 S. Nakamura, Security Eng.</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>This policy establishes the cryptographic requirements for protecting organizational data at rest and in transit. It defines approved algorithms, key management procedures, and implementation requirements for all information systems operated by the organization. This policy implements NIST SP 800-111, NIST SP 800-52 Rev 2, and FIPS 140-3 requirements. For a plain-language overview of federal cryptographic standards, see the NIST Cryptographic Standards and Guidelines portal.</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>This policy applies to all information systems, applications, and data stores that process, transmit, or store CUI, PII, or data classified at FIPS 199 Moderate or High impact levels. It applies to all personnel with system administration, development, or data handling responsibilities. BYOD encryption requirements are addressed in conjunction with the Mobile Device Management Policy. For cloud-specific encryption inheritance, refer to the FedRAMP authorization documentation for each cloud service in use. For current FIPS 140-3 validated module listings, see the NIST Cryptographic Module Validation Program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Encryption_Policy_POL-ENC-2026-008.docx</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Appendix E - Revision History</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ENC05.001</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Added ENC05.001-002 for High-impact systems. Appendix C expanded. 2.1 07/01/2025 S. Nakamura, Security Eng. Updated TLS requirements to mandate 1.3 preference. Removed TLS 1.1. 2.0 01/20/2025 M. Johnson Aligned to FIPS 140-3. Replaced FIPS 140-2 references throughout.</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>This policy establishes the cryptographic requirements for protecting organizational data at rest and in transit. It defines approved algorithms, key management procedures, and implementation requirements for all information systems operated by the organization. This policy implements NIST SP 800-111, NIST SP 800-52 Rev 2, and FIPS 140-3 requirements. For a plain-language overview of federal cryptographic standards, see the NIST Cryptographic Standards and Guidelines portal.</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>This policy applies to all information systems, applications, and data stores that process, transmit, or store CUI, PII, or data classified at FIPS 199 Moderate or High impact levels. It applies to all personnel with system administration, development, or data handling responsibilities. BYOD encryption requirements are addressed in conjunction with the Mobile Device Management Policy. For cloud-specific encryption inheritance, refer to the FedRAMP authorization documentation for each cloud service in use. For current FIPS 140-3 validated module listings, see the NIST Cryptographic Module Validation Program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Incident_Response_Policy_POL-IR-2026-003.docx</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Appendix A - References</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>IRP10.001</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>IRP10.001 The organization shall maintain an incident response plan that is reviewed and updated annually. IR-1 Implemented</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>1.0 Purpose This policy defines the requirements and procedures for identifying, reporting, containing, and recovering from information security incidents affecting organizational information systems and data.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2.0 Scope</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>This policy applies to all information security incidents involving organizational systems, whether hosted on-premises, in cloud environments, or managed by third-party service providers. For the definition of what constitutes a reportable incident, refer to Section 4 of this document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Incident_Response_Policy_POL-IR-2026-003.docx</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Appendix A - References</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>IRP10.002</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>IRP10.002 Incident response training shall be provided to all SOC personnel within 30 days of onboarding and annually thereafter. IR-2 Implemented</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>1.0 Purpose This policy defines the requirements and procedures for identifying, reporting, containing, and recovering from information security incidents affecting organizational information systems and data.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2.0 Scope</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>This policy applies to all information security incidents involving organizational systems, whether hosted on-premises, in cloud environments, or managed by third-party service providers. For the definition of what constitutes a reportable incident, refer to Section 4 of this document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Incident_Response_Policy_POL-IR-2026-003.docx</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Appendix A - References</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>IRP11.001</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>IRP11.001 Incident response testing shall be conducted at least annually through tabletop exercises or functional drills. IR-3 Implemented</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>1.0 Purpose This policy defines the requirements and procedures for identifying, reporting, containing, and recovering from information security incidents affecting organizational information systems and data.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2.0 Scope</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>This policy applies to all information security incidents involving organizational systems, whether hosted on-premises, in cloud environments, or managed by third-party service providers. For the definition of what constitutes a reportable incident, refer to Section 4 of this document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Incident_Response_Policy_POL-IR-2026-003.docx</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Appendix A - References</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>IRP11.002</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>IRP11.002 Automated incident detection mechanisms shall be deployed on all boundary and critical systems. IR-4 Partially Implemented</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>1.0 Purpose This policy defines the requirements and procedures for identifying, reporting, containing, and recovering from information security incidents affecting organizational information systems and data.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2.0 Scope</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>This policy applies to all information security incidents involving organizational systems, whether hosted on-premises, in cloud environments, or managed by third-party service providers. For the definition of what constitutes a reportable incident, refer to Section 4 of this document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Incident_Response_Policy_POL-IR-2026-003.docx</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Appendix A - References</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>IRP12.001</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>IRP12.001 All confirmed incidents shall be reported to CISA in accordance with federal reporting timelines. See the CISA Incident Reporting Guide referenced in Appendix A. IR-6 Implemented</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>1.0 Purpose This policy defines the requirements and procedures for identifying, reporting, containing, and recovering from information security incidents affecting organizational information systems and data.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2.0 Scope</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>This policy applies to all information security incidents involving organizational systems, whether hosted on-premises, in cloud environments, or managed by third-party service providers. For the definition of what constitutes a reportable incident, refer to Section 4 of this document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Incident_Response_example demo-2026-003 copy.docx</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Controls</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>IRP02.001</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>The following controls govern incident response operations. All controls map to NIST SP 800-53 Rev 5. Appendix C contains the severity classification matrix referenced by IRP02.001.</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>This policy establishes the incident response requirements for all information systems operated by the organization. It defines the processes, responsibilities, and technical controls necessary to detect, contain, eradicate, and recover from cybersecurity incidents affecting organizational assets and data. For NIST IR control family guidance, see the NIST SP 800-61 Rev 3 overview.</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>This policy applies to all employees, contractors, and third-party personnel who operate or support organizational IT systems. It covers all incidents affecting systems classified as FIPS 199 Low, Moderate, or High. For personnel onboarding requirements related to IR awareness, refer to the Security Awareness Training resources. Mobile device incidents are addressed in conjunction with the Mobile Device Management Policy. Cloud-specific incident procedures are addressed in Appendix A, Section 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Incident_Response_example demo-2026-003 copy.docx</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>IRP01.001</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>IRP01.001 IR Plan Development The organization shall develop and maintain a formal incident response plan reviewed annually. See Appendix A for the IR plan template. IR-8 Implemented IR Team</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>This policy establishes the incident response requirements for all information systems operated by the organization. It defines the processes, responsibilities, and technical controls necessary to detect, contain, eradicate, and recover from cybersecurity incidents affecting organizational assets and data. For NIST IR control family guidance, see the NIST SP 800-61 Rev 3 overview.</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>This policy applies to all employees, contractors, and third-party personnel who operate or support organizational IT systems. It covers all incidents affecting systems classified as FIPS 199 Low, Moderate, or High. For personnel onboarding requirements related to IR awareness, refer to the Security Awareness Training resources. Mobile device incidents are addressed in conjunction with the Mobile Device Management Policy. Cloud-specific incident procedures are addressed in Appendix A, Section 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Incident_Response_example demo-2026-003 copy.docx</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>IRP01.002</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>IRP01.002 IR Team Activation The IR team shall be activated within 1 hour of a P1 incident declaration. Refer to Appendix B for escalation contacts. IR-4 Implemented SOC</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>This policy establishes the incident response requirements for all information systems operated by the organization. It defines the processes, responsibilities, and technical controls necessary to detect, contain, eradicate, and recover from cybersecurity incidents affecting organizational assets and data. For NIST IR control family guidance, see the NIST SP 800-61 Rev 3 overview.</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>This policy applies to all employees, contractors, and third-party personnel who operate or support organizational IT systems. It covers all incidents affecting systems classified as FIPS 199 Low, Moderate, or High. For personnel onboarding requirements related to IR awareness, refer to the Security Awareness Training resources. Mobile device incidents are addressed in conjunction with the Mobile Device Management Policy. Cloud-specific incident procedures are addressed in Appendix A, Section 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Incident_Response_example demo-2026-003 copy.docx</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>IRP02.001</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>IRP02.001 Incident Classification All incidents shall be classified per the severity matrix in Appendix C before response actions begin. IR-5 Implemented SOC</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>This policy establishes the incident response requirements for all information systems operated by the organization. It defines the processes, responsibilities, and technical controls necessary to detect, contain, eradicate, and recover from cybersecurity incidents affecting organizational assets and data. For NIST IR control family guidance, see the NIST SP 800-61 Rev 3 overview.</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>This policy applies to all employees, contractors, and third-party personnel who operate or support organizational IT systems. It covers all incidents affecting systems classified as FIPS 199 Low, Moderate, or High. For personnel onboarding requirements related to IR awareness, refer to the Security Awareness Training resources. Mobile device incidents are addressed in conjunction with the Mobile Device Management Policy. Cloud-specific incident procedures are addressed in Appendix A, Section 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Incident_Response_example demo-2026-003 copy.docx</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>IRP02.002</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>IRP02.002 Evidence Preservation Digital evidence shall be preserved per the chain-of-custody procedures in Appendix D. Refer to Section 4.2 for legal hold requirements. IR-4(1) Implemented Forensics</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>This policy establishes the incident response requirements for all information systems operated by the organization. It defines the processes, responsibilities, and technical controls necessary to detect, contain, eradicate, and recover from cybersecurity incidents affecting organizational assets and data. For NIST IR control family guidance, see the NIST SP 800-61 Rev 3 overview.</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>This policy applies to all employees, contractors, and third-party personnel who operate or support organizational IT systems. It covers all incidents affecting systems classified as FIPS 199 Low, Moderate, or High. For personnel onboarding requirements related to IR awareness, refer to the Security Awareness Training resources. Mobile device incidents are addressed in conjunction with the Mobile Device Management Policy. Cloud-specific incident procedures are addressed in Appendix A, Section 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Incident_Response_example demo-2026-003 copy.docx</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>IRP03.001</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>IRP03.001 Incident Notification Incidents affecting CUI shall be reported to US-CERT within 1 hour of detection per CISA requirements. See Appendix E for notification templates. IR-6 Implemented ISSO</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>This policy establishes the incident response requirements for all information systems operated by the organization. It defines the processes, responsibilities, and technical controls necessary to detect, contain, eradicate, and recover from cybersecurity incidents affecting organizational assets and data. For NIST IR control family guidance, see the NIST SP 800-61 Rev 3 overview.</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>This policy applies to all employees, contractors, and third-party personnel who operate or support organizational IT systems. It covers all incidents affecting systems classified as FIPS 199 Low, Moderate, or High. For personnel onboarding requirements related to IR awareness, refer to the Security Awareness Training resources. Mobile device incidents are addressed in conjunction with the Mobile Device Management Policy. Cloud-specific incident procedures are addressed in Appendix A, Section 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Incident_Response_example demo-2026-003 copy.docx</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>IRP03.002</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>IRP03.002 After-Action Review A post-incident review shall be conducted within 5 business days. Findings shall feed into the risk register per the Risk Management Policy. IR-4(6) Partially Implemented IR Team</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>This policy establishes the incident response requirements for all information systems operated by the organization. It defines the processes, responsibilities, and technical controls necessary to detect, contain, eradicate, and recover from cybersecurity incidents affecting organizational assets and data. For NIST IR control family guidance, see the NIST SP 800-61 Rev 3 overview.</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>This policy applies to all employees, contractors, and third-party personnel who operate or support organizational IT systems. It covers all incidents affecting systems classified as FIPS 199 Low, Moderate, or High. For personnel onboarding requirements related to IR awareness, refer to the Security Awareness Training resources. Mobile device incidents are addressed in conjunction with the Mobile Device Management Policy. Cloud-specific incident procedures are addressed in Appendix A, Section 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Incident_Response_example demo-2026-003 copy.docx</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>IRP04.001</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>IRP04.001 Forensic Capability The organization shall maintain forensic tools and trained personnel capable of analyzing endpoints, network logs, and cloud environments. IR-4(14) Implemented Forensics</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>This policy establishes the incident response requirements for all information systems operated by the organization. It defines the processes, responsibilities, and technical controls necessary to detect, contain, eradicate, and recover from cybersecurity incidents affecting organizational assets and data. For NIST IR control family guidance, see the NIST SP 800-61 Rev 3 overview.</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>This policy applies to all employees, contractors, and third-party personnel who operate or support organizational IT systems. It covers all incidents affecting systems classified as FIPS 199 Low, Moderate, or High. For personnel onboarding requirements related to IR awareness, refer to the Security Awareness Training resources. Mobile device incidents are addressed in conjunction with the Mobile Device Management Policy. Cloud-specific incident procedures are addressed in Appendix A, Section 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Incident_Response_example demo-2026-003 copy.docx</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>IRP04.002</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>IRP04.002 Tabletop Exercises IR tabletop exercises shall be conducted semi-annually. Results shall be documented and stored in SharePoint per Appendix F. IR-3(2) Implemented IR Team Level Name Definition Notification SLA Response SLA P1 Critical Active exfiltration or system compromise. CUI at risk. 1 hour to US-CERT Immediate activation P2 High Confirmed malware, unauthorized privileged access. 4 hours internal 2 hours P3 Medium Suspected compromise, policy violation with data risk. 24 hours internal 8 business hours P4 Low Policy violation, no data impact, no active threat. 72 hours internal Next business day Version Date Author Changes 2.1 01/01/2026 R. Torres, ISSO Added cloud-specific IR procedures to Appendix A 2.0 07/15/2025 R. Torres, ISSO Major revision for EO 14028 compliance 1.2 01/10/2025 M. Johnson Updated US-CERT notification timelines</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>This policy establishes the incident response requirements for all information systems operated by the organization. It defines the processes, responsibilities, and technical controls necessary to detect, contain, eradicate, and recover from cybersecurity incidents affecting organizational assets and data. For NIST IR control family guidance, see the NIST SP 800-61 Rev 3 overview.</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>This policy applies to all employees, contractors, and third-party personnel who operate or support organizational IT systems. It covers all incidents affecting systems classified as FIPS 199 Low, Moderate, or High. For personnel onboarding requirements related to IR awareness, refer to the Security Awareness Training resources. Mobile device incidents are addressed in conjunction with the Mobile Device Management Policy. Cloud-specific incident procedures are addressed in Appendix A, Section 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Privacy_PII_Handling_Policy_POL-PII-2026-012.docx</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>PII04.002</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>This policy applies to all systems, programs, and operations that collect or use PII from members of the public, employees, contractors, or other individuals. It applies to all personnel with access to or responsibility for systems processing PII. Third-party processors handling PII on behalf of the organization are bound by contractual privacy requirements and are subject to annual assessment per PII04.002. This policy covers PII in all formats: digital records, physical documents, audio/video recordings, and biometric data. Systems of Records subject to the Privacy Act are identified in the System of Records Notice (SORN) inventory maintained by the Privacy Officer.</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>This policy establishes the requirements for collecting, processing, storing, transmitting, and disposing of personally identifiable information (PII) across all organizational systems and operations. It implements the Privacy Act of 1974, OMB Circular A-130 Appendix II, and NIST SP 800-122 requirements for federal PII protection. For the NIST PII definition and categorization framework, see NIST SP 800-122 Guide to Protecting PII. For OMB privacy policy requirements applicable to federal agencies, see OMB Circular A-130 Managing Federal Information Resources.</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>This policy applies to all systems, programs, and operations that collect or use PII from members of the public, employees, contractors, or other individuals. It applies to all personnel with access to or responsibility for systems processing PII. Third-party processors handling PII on behalf of the organization are bound by contractual privacy requirements and are subject to annual assessment per PII04.002. This policy covers PII in all formats: digital records, physical documents, audio/video recordings, and biometric data. Systems of Records subject to the Privacy Act are identified in the System of Records Notice (SORN) inventory maintained by the Privacy Officer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Privacy_PII_Handling_Policy_POL-PII-2026-012.docx</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Section 3 - PII Collection and Minimization Controls</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>PII01.001</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>PII01.001 - Privacy Impact Assessment Requirement Requirement: Any new system, program, or significant modification to an existing system that collects, processes, or stores PII shall undergo a Privacy Impact Assessment (PIA) before deployment. PIAs shall be reviewed by the Privacy Officer and approved by the SAOP. PIAs shall be updated whenever a system change materially affects PII handling. The PIA template and completion guidance are in Appendix A. PIAs for systems collecting information from the public shall be posted publicly per OMB A-130 requirements. NIST Mapping: AR-2 Status: Implemented Owner: Privacy Officer / System Owners</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>This policy establishes the requirements for collecting, processing, storing, transmitting, and disposing of personally identifiable information (PII) across all organizational systems and operations. It implements the Privacy Act of 1974, OMB Circular A-130 Appendix II, and NIST SP 800-122 requirements for federal PII protection. For the NIST PII definition and categorization framework, see NIST SP 800-122 Guide to Protecting PII. For OMB privacy policy requirements applicable to federal agencies, see OMB Circular A-130 Managing Federal Information Resources.</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>This policy applies to all systems, programs, and operations that collect or use PII from members of the public, employees, contractors, or other individuals. It applies to all personnel with access to or responsibility for systems processing PII. Third-party processors handling PII on behalf of the organization are bound by contractual privacy requirements and are subject to annual assessment per PII04.002. This policy covers PII in all formats: digital records, physical documents, audio/video recordings, and biometric data. Systems of Records subject to the Privacy Act are identified in the System of Records Notice (SORN) inventory maintained by the Privacy Officer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Privacy_PII_Handling_Policy_POL-PII-2026-012.docx</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Section 3 - PII Collection and Minimization Controls</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>PII01.002</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>PII01.002 - PII Minimization and Purpose Limitation Requirement: Systems shall collect only the PII categories necessary to accomplish the documented mission purpose. PII collected for one purpose shall not be used for a materially different purpose without re-evaluation against the original authority and a determination that the secondary use is compatible. The PII data elements authorized for each system are documented in the PIA and the System of Records Notice (SORN) referenced in Appendix B. Unauthorized PII collection discovered during audits shall be reported to the Privacy Officer within 24 hours. NIST Mapping: DI-1, UL-1 Status: Implemented Owner: Privacy Officer / System Owners</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>This policy establishes the requirements for collecting, processing, storing, transmitting, and disposing of personally identifiable information (PII) across all organizational systems and operations. It implements the Privacy Act of 1974, OMB Circular A-130 Appendix II, and NIST SP 800-122 requirements for federal PII protection. For the NIST PII definition and categorization framework, see NIST SP 800-122 Guide to Protecting PII. For OMB privacy policy requirements applicable to federal agencies, see OMB Circular A-130 Managing Federal Information Resources.</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>This policy applies to all systems, programs, and operations that collect or use PII from members of the public, employees, contractors, or other individuals. It applies to all personnel with access to or responsibility for systems processing PII. Third-party processors handling PII on behalf of the organization are bound by contractual privacy requirements and are subject to annual assessment per PII04.002. This policy covers PII in all formats: digital records, physical documents, audio/video recordings, and biometric data. Systems of Records subject to the Privacy Act are identified in the System of Records Notice (SORN) inventory maintained by the Privacy Officer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Privacy_PII_Handling_Policy_POL-PII-2026-012.docx</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Section 4 - PII Transmission and Storage Controls</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>ENC01.001</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>The following controls govern how PII is protected during storage and transmission. These controls work in conjunction with the Encryption Policy (POL-ENC-2026-008). All PII in transit shall be encrypted per ENC02.001. All PII at rest shall be encrypted per ENC01.001 or ENC01.002 depending on the storage type. Physical PII handling requirements are in Appendix C.</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>This policy establishes the requirements for collecting, processing, storing, transmitting, and disposing of personally identifiable information (PII) across all organizational systems and operations. It implements the Privacy Act of 1974, OMB Circular A-130 Appendix II, and NIST SP 800-122 requirements for federal PII protection. For the NIST PII definition and categorization framework, see NIST SP 800-122 Guide to Protecting PII. For OMB privacy policy requirements applicable to federal agencies, see OMB Circular A-130 Managing Federal Information Resources.</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>This policy applies to all systems, programs, and operations that collect or use PII from members of the public, employees, contractors, or other individuals. It applies to all personnel with access to or responsibility for systems processing PII. Third-party processors handling PII on behalf of the organization are bound by contractual privacy requirements and are subject to annual assessment per PII04.002. This policy covers PII in all formats: digital records, physical documents, audio/video recordings, and biometric data. Systems of Records subject to the Privacy Act are identified in the System of Records Notice (SORN) inventory maintained by the Privacy Officer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Privacy_PII_Handling_Policy_POL-PII-2026-012.docx</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Section 4 - PII Transmission and Storage Controls</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ENC01.002</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>The following controls govern how PII is protected during storage and transmission. These controls work in conjunction with the Encryption Policy (POL-ENC-2026-008). All PII in transit shall be encrypted per ENC02.001. All PII at rest shall be encrypted per ENC01.001 or ENC01.002 depending on the storage type. Physical PII handling requirements are in Appendix C.</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>This policy establishes the requirements for collecting, processing, storing, transmitting, and disposing of personally identifiable information (PII) across all organizational systems and operations. It implements the Privacy Act of 1974, OMB Circular A-130 Appendix II, and NIST SP 800-122 requirements for federal PII protection. For the NIST PII definition and categorization framework, see NIST SP 800-122 Guide to Protecting PII. For OMB privacy policy requirements applicable to federal agencies, see OMB Circular A-130 Managing Federal Information Resources.</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>This policy applies to all systems, programs, and operations that collect or use PII from members of the public, employees, contractors, or other individuals. It applies to all personnel with access to or responsibility for systems processing PII. Third-party processors handling PII on behalf of the organization are bound by contractual privacy requirements and are subject to annual assessment per PII04.002. This policy covers PII in all formats: digital records, physical documents, audio/video recordings, and biometric data. Systems of Records subject to the Privacy Act are identified in the System of Records Notice (SORN) inventory maintained by the Privacy Officer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Privacy_PII_Handling_Policy_POL-PII-2026-012.docx</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Section 4 - PII Transmission and Storage Controls</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ENC02.001</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>The following controls govern how PII is protected during storage and transmission. These controls work in conjunction with the Encryption Policy (POL-ENC-2026-008). All PII in transit shall be encrypted per ENC02.001. All PII at rest shall be encrypted per ENC01.001 or ENC01.002 depending on the storage type. Physical PII handling requirements are in Appendix C.</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>This policy establishes the requirements for collecting, processing, storing, transmitting, and disposing of personally identifiable information (PII) across all organizational systems and operations. It implements the Privacy Act of 1974, OMB Circular A-130 Appendix II, and NIST SP 800-122 requirements for federal PII protection. For the NIST PII definition and categorization framework, see NIST SP 800-122 Guide to Protecting PII. For OMB privacy policy requirements applicable to federal agencies, see OMB Circular A-130 Managing Federal Information Resources.</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>This policy applies to all systems, programs, and operations that collect or use PII from members of the public, employees, contractors, or other individuals. It applies to all personnel with access to or responsibility for systems processing PII. Third-party processors handling PII on behalf of the organization are bound by contractual privacy requirements and are subject to annual assessment per PII04.002. This policy covers PII in all formats: digital records, physical documents, audio/video recordings, and biometric data. Systems of Records subject to the Privacy Act are identified in the System of Records Notice (SORN) inventory maintained by the Privacy Officer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Privacy_PII_Handling_Policy_POL-PII-2026-012.docx</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Section 4 - PII Transmission and Storage Controls</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>PII02.001</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>PII02.001 - PII Labeling and Handling Requirement: Documents, files, and records containing PII shall be labeled with the appropriate sensitivity marking at creation. Digital files shall use the CUI//PRVCY sensitivity label in Microsoft Purview per the DLP Standard (STD-DLP-2026-011), Appendix C. Physical documents containing PII shall be marked in accordance with the organization's physical security requirements. Unlabeled documents discovered during audits shall be evaluated by the Privacy Officer to determine if PII is present and labeled accordingly. NIST Mapping: MP-3, DI-2 Status: Implemented Owner: All Personnel</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>This policy establishes the requirements for collecting, processing, storing, transmitting, and disposing of personally identifiable information (PII) across all organizational systems and operations. It implements the Privacy Act of 1974, OMB Circular A-130 Appendix II, and NIST SP 800-122 requirements for federal PII protection. For the NIST PII definition and categorization framework, see NIST SP 800-122 Guide to Protecting PII. For OMB privacy policy requirements applicable to federal agencies, see OMB Circular A-130 Managing Federal Information Resources.</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>This policy applies to all systems, programs, and operations that collect or use PII from members of the public, employees, contractors, or other individuals. It applies to all personnel with access to or responsibility for systems processing PII. Third-party processors handling PII on behalf of the organization are bound by contractual privacy requirements and are subject to annual assessment per PII04.002. This policy covers PII in all formats: digital records, physical documents, audio/video recordings, and biometric data. Systems of Records subject to the Privacy Act are identified in the System of Records Notice (SORN) inventory maintained by the Privacy Officer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Privacy_PII_Handling_Policy_POL-PII-2026-012.docx</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Section 4 - PII Transmission and Storage Controls</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>PII02.002</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>PII02.002 - PII Sharing and Disclosure Controls Requirement: PII shall not be disclosed externally without: (a) a routine use identified in the applicable SORN, (b) written consent from the individual, (c) a court order or legal mandate, or (d) a written data sharing agreement approved by the Privacy Officer and legal counsel. Verbal disclosures of PII for law enforcement or other purposes shall be documented in writing within 24 hours. The disclosure log template is in Appendix D. For inter-agency data sharing, use the approved Data Sharing Agreement template referenced in Appendix D. NIST Mapping: AP-2, UL-2 Status: Partially Implemented Owner: Privacy Officer / Legal</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>This policy establishes the requirements for collecting, processing, storing, transmitting, and disposing of personally identifiable information (PII) across all organizational systems and operations. It implements the Privacy Act of 1974, OMB Circular A-130 Appendix II, and NIST SP 800-122 requirements for federal PII protection. For the NIST PII definition and categorization framework, see NIST SP 800-122 Guide to Protecting PII. For OMB privacy policy requirements applicable to federal agencies, see OMB Circular A-130 Managing Federal Information Resources.</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>This policy applies to all systems, programs, and operations that collect or use PII from members of the public, employees, contractors, or other individuals. It applies to all personnel with access to or responsibility for systems processing PII. Third-party processors handling PII on behalf of the organization are bound by contractual privacy requirements and are subject to annual assessment per PII04.002. This policy covers PII in all formats: digital records, physical documents, audio/video recordings, and biometric data. Systems of Records subject to the Privacy Act are identified in the System of Records Notice (SORN) inventory maintained by the Privacy Officer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Privacy_PII_Handling_Policy_POL-PII-2026-012.docx</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Appendix A - Privacy Impact Assessment Requirements and Template</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>PII01.001</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>This appendix provides the PIA template referenced in PII01.001 and two additional controls governing PIA review timelines and public posting requirements. The PIA template is available in SharePoint under Privacy Program documents.</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>This policy establishes the requirements for collecting, processing, storing, transmitting, and disposing of personally identifiable information (PII) across all organizational systems and operations. It implements the Privacy Act of 1974, OMB Circular A-130 Appendix II, and NIST SP 800-122 requirements for federal PII protection. For the NIST PII definition and categorization framework, see NIST SP 800-122 Guide to Protecting PII. For OMB privacy policy requirements applicable to federal agencies, see OMB Circular A-130 Managing Federal Information Resources.</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>This policy applies to all systems, programs, and operations that collect or use PII from members of the public, employees, contractors, or other individuals. It applies to all personnel with access to or responsibility for systems processing PII. Third-party processors handling PII on behalf of the organization are bound by contractual privacy requirements and are subject to annual assessment per PII04.002. This policy covers PII in all formats: digital records, physical documents, audio/video recordings, and biometric data. Systems of Records subject to the Privacy Act are identified in the System of Records Notice (SORN) inventory maintained by the Privacy Officer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Privacy_PII_Handling_Policy_POL-PII-2026-012.docx</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Appendix A Controls - PIA Process Requirements</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>PII01.001</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>The following controls govern the PIA process workflow for system owners and the Privacy Officer. These supplement PII01.001 with process-level requirements.</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>This policy establishes the requirements for collecting, processing, storing, transmitting, and disposing of personally identifiable information (PII) across all organizational systems and operations. It implements the Privacy Act of 1974, OMB Circular A-130 Appendix II, and NIST SP 800-122 requirements for federal PII protection. For the NIST PII definition and categorization framework, see NIST SP 800-122 Guide to Protecting PII. For OMB privacy policy requirements applicable to federal agencies, see OMB Circular A-130 Managing Federal Information Resources.</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>This policy applies to all systems, programs, and operations that collect or use PII from members of the public, employees, contractors, or other individuals. It applies to all personnel with access to or responsibility for systems processing PII. Third-party processors handling PII on behalf of the organization are bound by contractual privacy requirements and are subject to annual assessment per PII04.002. This policy covers PII in all formats: digital records, physical documents, audio/video recordings, and biometric data. Systems of Records subject to the Privacy Act are identified in the System of Records Notice (SORN) inventory maintained by the Privacy Officer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Privacy_PII_Handling_Policy_POL-PII-2026-012.docx</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Appendix A Controls - PIA Process Requirements</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>PII05.001</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>PII05.001 - PIA Review and Approval Timeline Requirement: System owners shall submit draft PIAs to the Privacy Officer no later than 60 days before a system's planned deployment or significant modification. The Privacy Officer shall complete PIA review within 20 business days of receiving a complete draft. If the PIA requires revisions, the system owner has 10 business days to respond. Systems shall not be deployed or significantly modified until PIA approval is documented. Emergency exemptions require SAOP written approval and shall not exceed 30 days. NIST Mapping: AR-2 Status: Implemented Owner: Privacy Officer / System Owners</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>This policy establishes the requirements for collecting, processing, storing, transmitting, and disposing of personally identifiable information (PII) across all organizational systems and operations. It implements the Privacy Act of 1974, OMB Circular A-130 Appendix II, and NIST SP 800-122 requirements for federal PII protection. For the NIST PII definition and categorization framework, see NIST SP 800-122 Guide to Protecting PII. For OMB privacy policy requirements applicable to federal agencies, see OMB Circular A-130 Managing Federal Information Resources.</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>This policy applies to all systems, programs, and operations that collect or use PII from members of the public, employees, contractors, or other individuals. It applies to all personnel with access to or responsibility for systems processing PII. Third-party processors handling PII on behalf of the organization are bound by contractual privacy requirements and are subject to annual assessment per PII04.002. This policy covers PII in all formats: digital records, physical documents, audio/video recordings, and biometric data. Systems of Records subject to the Privacy Act are identified in the System of Records Notice (SORN) inventory maintained by the Privacy Officer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Privacy_PII_Handling_Policy_POL-PII-2026-012.docx</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Appendix A Controls - PIA Process Requirements</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>PII05.002</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>PII05.002 - System of Records Notice (SORN) Maintenance Requirement: Systems of Records subject to the Privacy Act shall have a current SORN published in the Federal Register. SORNs shall be reviewed annually by the Privacy Officer and updated when system changes materially affect the routine uses, categories of individuals, or categories of records. New SORNs or amendments require a 30-day public comment period unless exempted. The SORN inventory is maintained in Appendix B and reviewed quarterly. NIST Mapping: UL-1, TR-2 Status: Implemented Owner: Privacy Officer / Legal</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>This policy establishes the requirements for collecting, processing, storing, transmitting, and disposing of personally identifiable information (PII) across all organizational systems and operations. It implements the Privacy Act of 1974, OMB Circular A-130 Appendix II, and NIST SP 800-122 requirements for federal PII protection. For the NIST PII definition and categorization framework, see NIST SP 800-122 Guide to Protecting PII. For OMB privacy policy requirements applicable to federal agencies, see OMB Circular A-130 Managing Federal Information Resources.</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>This policy applies to all systems, programs, and operations that collect or use PII from members of the public, employees, contractors, or other individuals. It applies to all personnel with access to or responsibility for systems processing PII. Third-party processors handling PII on behalf of the organization are bound by contractual privacy requirements and are subject to annual assessment per PII04.002. This policy covers PII in all formats: digital records, physical documents, audio/video recordings, and biometric data. Systems of Records subject to the Privacy Act are identified in the System of Records Notice (SORN) inventory maintained by the Privacy Officer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Privacy_PII_Handling_Policy_POL-PII-2026-012.docx</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Appendix F - Revision History</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>PII03.001</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>PII03.001 PII Breach Detection and Reporting</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>This policy establishes the requirements for collecting, processing, storing, transmitting, and disposing of personally identifiable information (PII) across all organizational systems and operations. It implements the Privacy Act of 1974, OMB Circular A-130 Appendix II, and NIST SP 800-122 requirements for federal PII protection. For the NIST PII definition and categorization framework, see NIST SP 800-122 Guide to Protecting PII. For OMB privacy policy requirements applicable to federal agencies, see OMB Circular A-130 Managing Federal Information Resources.</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>This policy applies to all systems, programs, and operations that collect or use PII from members of the public, employees, contractors, or other individuals. It applies to all personnel with access to or responsibility for systems processing PII. Third-party processors handling PII on behalf of the organization are bound by contractual privacy requirements and are subject to annual assessment per PII04.002. This policy covers PII in all formats: digital records, physical documents, audio/video recordings, and biometric data. Systems of Records subject to the Privacy Act are identified in the System of Records Notice (SORN) inventory maintained by the Privacy Officer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Privacy_PII_Handling_Policy_POL-PII-2026-012.docx</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Appendix F - Revision History</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>PII03.002</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Suspected PII breaches shall be reported to the Privacy Officer and SOC within 1 hour of discovery by any personnel who identifies or suspects a breach. The Privacy Officer shall make a preliminary breach determination within 2 hours. Breach notification timelines in PII03.002 begin at the time of the preliminary determination, not at confirmed verification. IR-6, AR-6 Implemented All Personnel / Privacy Officer</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>This policy establishes the requirements for collecting, processing, storing, transmitting, and disposing of personally identifiable information (PII) across all organizational systems and operations. It implements the Privacy Act of 1974, OMB Circular A-130 Appendix II, and NIST SP 800-122 requirements for federal PII protection. For the NIST PII definition and categorization framework, see NIST SP 800-122 Guide to Protecting PII. For OMB privacy policy requirements applicable to federal agencies, see OMB Circular A-130 Managing Federal Information Resources.</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>This policy applies to all systems, programs, and operations that collect or use PII from members of the public, employees, contractors, or other individuals. It applies to all personnel with access to or responsibility for systems processing PII. Third-party processors handling PII on behalf of the organization are bound by contractual privacy requirements and are subject to annual assessment per PII04.002. This policy covers PII in all formats: digital records, physical documents, audio/video recordings, and biometric data. Systems of Records subject to the Privacy Act are identified in the System of Records Notice (SORN) inventory maintained by the Privacy Officer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Privacy_PII_Handling_Policy_POL-PII-2026-012.docx</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Appendix F - Revision History</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>PII03.002</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>PII03.002 Federal Breach Notification Timelines Confirmed PII breaches shall be reported to US-CERT within 1 hour per OMB M-17-12. The SAOP shall be notified within 1 hour. Affected individuals shall be notified within 10 business days unless law enforcement requests a delay. Congressional notification follows agency procedures. See Appendix E for notification templates and contact information. IR-6 Implemented Privacy Officer / ISSO</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>This policy establishes the requirements for collecting, processing, storing, transmitting, and disposing of personally identifiable information (PII) across all organizational systems and operations. It implements the Privacy Act of 1974, OMB Circular A-130 Appendix II, and NIST SP 800-122 requirements for federal PII protection. For the NIST PII definition and categorization framework, see NIST SP 800-122 Guide to Protecting PII. For OMB privacy policy requirements applicable to federal agencies, see OMB Circular A-130 Managing Federal Information Resources.</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>This policy applies to all systems, programs, and operations that collect or use PII from members of the public, employees, contractors, or other individuals. It applies to all personnel with access to or responsibility for systems processing PII. Third-party processors handling PII on behalf of the organization are bound by contractual privacy requirements and are subject to annual assessment per PII04.002. This policy covers PII in all formats: digital records, physical documents, audio/video recordings, and biometric data. Systems of Records subject to the Privacy Act are identified in the System of Records Notice (SORN) inventory maintained by the Privacy Officer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Privacy_PII_Handling_Policy_POL-PII-2026-012.docx</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Appendix F - Revision History</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>PII04.001</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>PII04.001 PII Breach Risk Assessment Following a breach determination, the Privacy Officer shall conduct a risk assessment within 24 hours to determine: the nature and extent of PII compromised, the likelihood of harm to affected individuals, and whether substitute notice is appropriate. Risk assessments shall document harm categories per OMB M-17-12 Appendix C definitions. Results shall be retained per the Records Retention Policy. RA-3, AR-6 Implemented Privacy Officer</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>This policy establishes the requirements for collecting, processing, storing, transmitting, and disposing of personally identifiable information (PII) across all organizational systems and operations. It implements the Privacy Act of 1974, OMB Circular A-130 Appendix II, and NIST SP 800-122 requirements for federal PII protection. For the NIST PII definition and categorization framework, see NIST SP 800-122 Guide to Protecting PII. For OMB privacy policy requirements applicable to federal agencies, see OMB Circular A-130 Managing Federal Information Resources.</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>This policy applies to all systems, programs, and operations that collect or use PII from members of the public, employees, contractors, or other individuals. It applies to all personnel with access to or responsibility for systems processing PII. Third-party processors handling PII on behalf of the organization are bound by contractual privacy requirements and are subject to annual assessment per PII04.002. This policy covers PII in all formats: digital records, physical documents, audio/video recordings, and biometric data. Systems of Records subject to the Privacy Act are identified in the System of Records Notice (SORN) inventory maintained by the Privacy Officer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Privacy_PII_Handling_Policy_POL-PII-2026-012.docx</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Appendix F - Revision History</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>PII04.002</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>PII04.002 Third-Party PII Processor Oversight Third-party processors handling PII shall be assessed annually for privacy compliance. Assessments shall verify: data processing agreement (DPA) currency, security controls commensurate with PII sensitivity, subprocessor transparency, and breach notification contractual obligations. Assessment results shall be reviewed by the Privacy Officer and reported to the CISO quarterly. SA-9, AR-3 Partially Implemented Privacy Officer / Procurement SORN ID System Name PII Categories Last Published [ORG]-001 Personnel Records System Name, SSN, employment history, performance data January 2025 [ORG]-002 Public Benefits Tracking System Name, address, income, eligibility determinations March 2024 [ORG]-003 IT Access Management System Name, user ID, access roles, authentication events July 2024 Version Date Author Changes 1.1 03/01/2026 C. Rivera, Privacy Officer</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>This policy establishes the requirements for collecting, processing, storing, transmitting, and disposing of personally identifiable information (PII) across all organizational systems and operations. It implements the Privacy Act of 1974, OMB Circular A-130 Appendix II, and NIST SP 800-122 requirements for federal PII protection. For the NIST PII definition and categorization framework, see NIST SP 800-122 Guide to Protecting PII. For OMB privacy policy requirements applicable to federal agencies, see OMB Circular A-130 Managing Federal Information Resources.</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>This policy applies to all systems, programs, and operations that collect or use PII from members of the public, employees, contractors, or other individuals. It applies to all personnel with access to or responsibility for systems processing PII. Third-party processors handling PII on behalf of the organization are bound by contractual privacy requirements and are subject to annual assessment per PII04.002. This policy covers PII in all formats: digital records, physical documents, audio/video recordings, and biometric data. Systems of Records subject to the Privacy Act are identified in the System of Records Notice (SORN) inventory maintained by the Privacy Officer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Privacy_PII_Handling_Policy_POL-PII-2026-012.docx</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Appendix F - Revision History</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>PII04.002</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Added third-party oversight control (PII04.002). Updated breach timelines for OMB M-17-12 alignment. 1.0 01/15/2026 C. Rivera, Privacy Officer Initial release. Implements Privacy Act, OMB A-130, and NIST SP 800-122.</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>This policy establishes the requirements for collecting, processing, storing, transmitting, and disposing of personally identifiable information (PII) across all organizational systems and operations. It implements the Privacy Act of 1974, OMB Circular A-130 Appendix II, and NIST SP 800-122 requirements for federal PII protection. For the NIST PII definition and categorization framework, see NIST SP 800-122 Guide to Protecting PII. For OMB privacy policy requirements applicable to federal agencies, see OMB Circular A-130 Managing Federal Information Resources.</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>This policy applies to all systems, programs, and operations that collect or use PII from members of the public, employees, contractors, or other individuals. It applies to all personnel with access to or responsibility for systems processing PII. Third-party processors handling PII on behalf of the organization are bound by contractual privacy requirements and are subject to annual assessment per PII04.002. This policy covers PII in all formats: digital records, physical documents, audio/video recordings, and biometric data. Systems of Records subject to the Privacy Act are identified in the System of Records Notice (SORN) inventory maintained by the Privacy Officer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ACC01.001</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ACC01.001 User Account Provisioning AC-2 CIS 5.1 AC-2 (Mod) Access Control Policy Implemented</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ACC01.002</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ACC01.002 Privileged Account Mgmt AC-6 CIS 5.4 AC-6 (Mod) Access Control Policy Implemented</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ACC02.001</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>ACC02.001 Remote Access Controls AC-17 CIS 12.7 AC-17 (Mod) Access Control Policy Implemented</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ACC02.002</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ACC02.002 Wireless Access AC-18 CIS 12.6 AC-18 (Mod) Access Control Policy Partial</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ACC03.001</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ACC03.001 Session Lock AC-11 CIS 4.3 AC-11 (Mod) Access Control Policy Implemented</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ACC03.002</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>ACC03.002 Session Termination AC-12 CIS 4.3 AC-12 (High) Access Control Policy Not Impl</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>SAR01.001</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>SAR01.001 RBAC for CUI AC-3 CIS 6.8 AC-3 (Mod) Access Control Policy Implemented</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>SAR01.002</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>SAR01.002 CUI Access Logging AC-4, AU-3 CIS 8.5 AU-3 (Mod) Access Control Policy Implemented</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>SAR02.001</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>SAR02.001 External CUI Connections AC-4 CIS 13.4 AC-4 (High) Access Control Policy Implemented Org Control Control Title NIST 800-53 CIS v8 FedRAMP Parent Policy Status</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>IRP10.001</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>IRP10.001 IR Plan Maintenance IR-1 CIS 17.1 IR-1 (Mod) Incident Response Policy Implemented</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>IRP10.002</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>IRP10.002 IR Training IR-2 CIS 17.2 IR-2 (Mod) Incident Response Policy Implemented</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>IRP11.001</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>IRP11.001 IR Testing IR-3 CIS 17.4 IR-3 (Mod) Incident Response Policy Implemented</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>IRP11.002</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>IRP11.002 Automated Detection IR-4 CIS 17.3 IR-4 (Mod) Incident Response Policy Partial</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>IRP12.001</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>IRP12.001 Incident Reporting IR-6 CIS 17.6 IR-6 (Mod) Incident Response Policy Implemented Org Control Control Title NIST 800-53 CIS v8 FedRAMP Parent Policy Status</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>CFG01.001</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>CFG01.001 Baseline Development CM-2 CIS 4.1 CM-2 (Mod) Config Mgmt Policy Implemented</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>CFG01.002</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>CFG01.002 Baseline Review CM-2(1) CIS 4.2 CM-2(1) (Mod) Config Mgmt Policy Implemented</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>CFG02.001</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>CFG02.001 Change Control CM-3 CIS 4.8 CM-3 (Mod) Config Mgmt Policy Implemented</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>CFG02.002</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>CFG02.002 Change Impact Analysis CM-4 CIS 4.8 CM-4 (Mod) Config Mgmt Policy Partial</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>CFG03.001</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>CFG03.001 Config Scanning CM-6 CIS 4.1 CM-6 (Mod) Config Mgmt Policy Implemented</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>CFG03.002</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>CFG03.002 Drift Detection CM-3(5) CIS 4.3 CM-3(5) (High) Config Mgmt Policy Not Impl</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>CFG04.001</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>CFG04.001 Software Inventory CM-7 CIS 2.1 CM-7 (Mod) Config Mgmt Policy Partial</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>CFG04.002</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>CFG04.002 App Whitelisting CM-7(5) CIS 2.6 CM-7(5) (High) Config Mgmt Policy Not Impl Org Control Inheritance Type Provider Provider Control Validation Method</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ACC01.001</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>ACC01.001 Hybrid Microsoft Azure Gov Azure AD provisioning Annual SSP review</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>CFG01.001</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>CFG01.001 Hybrid Microsoft Azure Gov Azure Policy baselines Quarterly scan comparison</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>IRP11.002</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>IRP11.002 Shared Microsoft Azure Gov Azure Sentinel alerts Monthly detection coverage review</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>RMF_Compliance_Mapping_POL-RMF-2026-010.docx</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>CFG03.001</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>CFG03.001 Hybrid Microsoft Defender Defender vulnerability scanning Weekly scan report review Term Definition Control Inheritance The practice of relying on security controls implemented by a shared service provider (e.g., cloud IaaS) rather than implementing them independently. Hybrid Control A control where responsibility is shared between the organization and a service provider. Both parties must implement their portion. FedRAMP Federal Risk and Authorization Management Program. A government-wide program that provides a standardized approach to security assessment for cloud products and services. STIG Security Technical Implementation Guide. Configuration standards published by DISA for hardening information systems. CIS Benchmark Configuration guidelines published by the Center for Internet Security for securing operating systems, applications, and network devices. POA&amp;M Plan of Action and Milestones. A document that identifies tasks needing accomplishment to resolve security weaknesses. SSP System Security Plan. A formal document that describes the security controls in place or planned for an information system. ATO Authorization to Operate. A formal declaration by a designated authority that an information system is authorized for operation. Version Date Changes 2.0 03/10/2026 Added Appendix D (Inheritance Matrix). Updated all crosswalks for FY2026 baseline review. 1.5 09/15/2025 Added CIS v8 mappings. Corrected FedRAMP baseline levels. 1.0 03/01/2025 Initial release.</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>This document provides the compliance mapping between organizational controls and external regulatory frameworks. It serves as the authoritative crosswalk for audit preparation, continuous monitoring, and control inheritance documentation.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>This mapping covers all controls defined in the organizational control catalog. For the complete control descriptions, refer to the individual policy documents (Access Control Policy, Incident Response Policy, Configuration Management Policy, etc.). This document maps controls only; it does not define requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Risk_Management_Policy_POL-RM-2026-009.docx</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>RMP04.001</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational systems regardless of impact level. It applies to all personnel with system ownership, security, or authorization responsibilities. Third-party providers handling CUI are subject to the risk assessment requirements in RMP04.001. For FedRAMP-specific risk management requirements applicable to cloud service providers, refer to the Cloud Security Policy and FedRAMP Risk Management documentation.</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>This policy establishes the risk management requirements for all information systems and organizational operations. It defines the processes for identifying, assessing, accepting, and mitigating risks to organizational information assets. This policy implements NIST RMF requirements and supports continuous ATO maintenance. For the NIST Risk Management Framework overview, see NIST RMF Quick Start Guide.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Third-party risk assessments shall evaluate: (1) Data access scope (CUI categories handled), (2) Security documentation (FedRAMP authorization, SOC 2 Type II, CMMC level), (3) Incident history, (4) Subcontractor reliance, (5) Data residency and jurisdiction, (6) Contractual security requirements and right-to-audit clauses. For current third-party assessment status, see the vendor risk register maintained by Procurement. FedRAMP marketplace verification: FedRAMP Marketplace.</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational systems regardless of impact level. It applies to all personnel with system ownership, security, or authorization responsibilities. Third-party providers handling CUI are subject to the risk assessment requirements in RMP04.001. For FedRAMP-specific risk management requirements applicable to cloud service providers, refer to the Cloud Security Policy and FedRAMP Risk Management documentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Risk_Management_Policy_POL-RM-2026-009.docx</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Controls</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>RMP03.001</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Controls are organized by risk management function. For the risk register template, see Appendix C. For POA&amp;M procedures, see Appendix E and RMP03.001.</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>This policy establishes the risk management requirements for all information systems and organizational operations. It defines the processes for identifying, assessing, accepting, and mitigating risks to organizational information assets. This policy implements NIST RMF requirements and supports continuous ATO maintenance. For the NIST Risk Management Framework overview, see NIST RMF Quick Start Guide.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Third-party risk assessments shall evaluate: (1) Data access scope (CUI categories handled), (2) Security documentation (FedRAMP authorization, SOC 2 Type II, CMMC level), (3) Incident history, (4) Subcontractor reliance, (5) Data residency and jurisdiction, (6) Contractual security requirements and right-to-audit clauses. For current third-party assessment status, see the vendor risk register maintained by Procurement. FedRAMP marketplace verification: FedRAMP Marketplace.</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational systems regardless of impact level. It applies to all personnel with system ownership, security, or authorization responsibilities. Third-party providers handling CUI are subject to the risk assessment requirements in RMP04.001. For FedRAMP-specific risk management requirements applicable to cloud service providers, refer to the Cloud Security Policy and FedRAMP Risk Management documentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Risk_Management_Policy_POL-RM-2026-009.docx</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>RMP01.001</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>RMP01.001 Risk Assessment Frequency Formal risk assessments shall be conducted annually and upon significant changes to systems or threat environment. See Appendix A for the risk assessment methodology. RA-3 Implemented ISSO</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>This policy establishes the risk management requirements for all information systems and organizational operations. It defines the processes for identifying, assessing, accepting, and mitigating risks to organizational information assets. This policy implements NIST RMF requirements and supports continuous ATO maintenance. For the NIST Risk Management Framework overview, see NIST RMF Quick Start Guide.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Third-party risk assessments shall evaluate: (1) Data access scope (CUI categories handled), (2) Security documentation (FedRAMP authorization, SOC 2 Type II, CMMC level), (3) Incident history, (4) Subcontractor reliance, (5) Data residency and jurisdiction, (6) Contractual security requirements and right-to-audit clauses. For current third-party assessment status, see the vendor risk register maintained by Procurement. FedRAMP marketplace verification: FedRAMP Marketplace.</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational systems regardless of impact level. It applies to all personnel with system ownership, security, or authorization responsibilities. Third-party providers handling CUI are subject to the risk assessment requirements in RMP04.001. For FedRAMP-specific risk management requirements applicable to cloud service providers, refer to the Cloud Security Policy and FedRAMP Risk Management documentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Risk_Management_Policy_POL-RM-2026-009.docx</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>RMP01.002</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>RMP01.002 Threat Identification The organization shall identify and document threats using current intelligence sources including CISA AIS and MS-ISAC. Appendix B documents all active threat intelligence sources. RA-3(1) Implemented Threat Intel</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>This policy establishes the risk management requirements for all information systems and organizational operations. It defines the processes for identifying, assessing, accepting, and mitigating risks to organizational information assets. This policy implements NIST RMF requirements and supports continuous ATO maintenance. For the NIST Risk Management Framework overview, see NIST RMF Quick Start Guide.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Third-party risk assessments shall evaluate: (1) Data access scope (CUI categories handled), (2) Security documentation (FedRAMP authorization, SOC 2 Type II, CMMC level), (3) Incident history, (4) Subcontractor reliance, (5) Data residency and jurisdiction, (6) Contractual security requirements and right-to-audit clauses. For current third-party assessment status, see the vendor risk register maintained by Procurement. FedRAMP marketplace verification: FedRAMP Marketplace.</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational systems regardless of impact level. It applies to all personnel with system ownership, security, or authorization responsibilities. Third-party providers handling CUI are subject to the risk assessment requirements in RMP04.001. For FedRAMP-specific risk management requirements applicable to cloud service providers, refer to the Cloud Security Policy and FedRAMP Risk Management documentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Risk_Management_Policy_POL-RM-2026-009.docx</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>RMP02.001</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>RMP02.001 Risk Register Maintenance A risk register shall be maintained and reviewed quarterly by the CISO. The register template is in Appendix C. Risk entries shall be linked to the controls in the relevant policy. PM-9 Implemented CISO</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>This policy establishes the risk management requirements for all information systems and organizational operations. It defines the processes for identifying, assessing, accepting, and mitigating risks to organizational information assets. This policy implements NIST RMF requirements and supports continuous ATO maintenance. For the NIST Risk Management Framework overview, see NIST RMF Quick Start Guide.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Third-party risk assessments shall evaluate: (1) Data access scope (CUI categories handled), (2) Security documentation (FedRAMP authorization, SOC 2 Type II, CMMC level), (3) Incident history, (4) Subcontractor reliance, (5) Data residency and jurisdiction, (6) Contractual security requirements and right-to-audit clauses. For current third-party assessment status, see the vendor risk register maintained by Procurement. FedRAMP marketplace verification: FedRAMP Marketplace.</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational systems regardless of impact level. It applies to all personnel with system ownership, security, or authorization responsibilities. Third-party providers handling CUI are subject to the risk assessment requirements in RMP04.001. For FedRAMP-specific risk management requirements applicable to cloud service providers, refer to the Cloud Security Policy and FedRAMP Risk Management documentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Risk_Management_Policy_POL-RM-2026-009.docx</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>RMP02.002</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>RMP02.002 Risk Acceptance Process Risks accepted rather than mitigated require documented ISSM and AO approval. Acceptance documentation format is in Appendix D. Accepted risks shall not exceed 18 months without re-evaluation. PM-9 Implemented AO</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>This policy establishes the risk management requirements for all information systems and organizational operations. It defines the processes for identifying, assessing, accepting, and mitigating risks to organizational information assets. This policy implements NIST RMF requirements and supports continuous ATO maintenance. For the NIST Risk Management Framework overview, see NIST RMF Quick Start Guide.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Third-party risk assessments shall evaluate: (1) Data access scope (CUI categories handled), (2) Security documentation (FedRAMP authorization, SOC 2 Type II, CMMC level), (3) Incident history, (4) Subcontractor reliance, (5) Data residency and jurisdiction, (6) Contractual security requirements and right-to-audit clauses. For current third-party assessment status, see the vendor risk register maintained by Procurement. FedRAMP marketplace verification: FedRAMP Marketplace.</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational systems regardless of impact level. It applies to all personnel with system ownership, security, or authorization responsibilities. Third-party providers handling CUI are subject to the risk assessment requirements in RMP04.001. For FedRAMP-specific risk management requirements applicable to cloud service providers, refer to the Cloud Security Policy and FedRAMP Risk Management documentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Risk_Management_Policy_POL-RM-2026-009.docx</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>RMP03.001</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>RMP03.001 POA&amp;M Management Plan of Action and Milestones (POA&amp;M) items shall be created for all findings from assessments, audits, and incident after-action reviews. POA&amp;M tracking template is in Appendix E. CA-5 Implemented ISSO</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>This policy establishes the risk management requirements for all information systems and organizational operations. It defines the processes for identifying, assessing, accepting, and mitigating risks to organizational information assets. This policy implements NIST RMF requirements and supports continuous ATO maintenance. For the NIST Risk Management Framework overview, see NIST RMF Quick Start Guide.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Third-party risk assessments shall evaluate: (1) Data access scope (CUI categories handled), (2) Security documentation (FedRAMP authorization, SOC 2 Type II, CMMC level), (3) Incident history, (4) Subcontractor reliance, (5) Data residency and jurisdiction, (6) Contractual security requirements and right-to-audit clauses. For current third-party assessment status, see the vendor risk register maintained by Procurement. FedRAMP marketplace verification: FedRAMP Marketplace.</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational systems regardless of impact level. It applies to all personnel with system ownership, security, or authorization responsibilities. Third-party providers handling CUI are subject to the risk assessment requirements in RMP04.001. For FedRAMP-specific risk management requirements applicable to cloud service providers, refer to the Cloud Security Policy and FedRAMP Risk Management documentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Risk_Management_Policy_POL-RM-2026-009.docx</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>RMP03.002</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>RMP03.002 Residual Risk Review After control implementation, residual risk shall be documented and reviewed by the ISSM before system authorization. See the System Authorization Policy for ATO requirements. RA-3 Implemented ISSM</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>This policy establishes the risk management requirements for all information systems and organizational operations. It defines the processes for identifying, assessing, accepting, and mitigating risks to organizational information assets. This policy implements NIST RMF requirements and supports continuous ATO maintenance. For the NIST Risk Management Framework overview, see NIST RMF Quick Start Guide.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Third-party risk assessments shall evaluate: (1) Data access scope (CUI categories handled), (2) Security documentation (FedRAMP authorization, SOC 2 Type II, CMMC level), (3) Incident history, (4) Subcontractor reliance, (5) Data residency and jurisdiction, (6) Contractual security requirements and right-to-audit clauses. For current third-party assessment status, see the vendor risk register maintained by Procurement. FedRAMP marketplace verification: FedRAMP Marketplace.</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational systems regardless of impact level. It applies to all personnel with system ownership, security, or authorization responsibilities. Third-party providers handling CUI are subject to the risk assessment requirements in RMP04.001. For FedRAMP-specific risk management requirements applicable to cloud service providers, refer to the Cloud Security Policy and FedRAMP Risk Management documentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Risk_Management_Policy_POL-RM-2026-009.docx</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>RMP04.001</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>RMP04.001 Third-Party Risk Assessment Third-party service providers handling CUI shall undergo risk assessment prior to contract award and annually thereafter. Assessment criteria are in Appendix F. SR-3 Partially Implemented Procurement</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>This policy establishes the risk management requirements for all information systems and organizational operations. It defines the processes for identifying, assessing, accepting, and mitigating risks to organizational information assets. This policy implements NIST RMF requirements and supports continuous ATO maintenance. For the NIST Risk Management Framework overview, see NIST RMF Quick Start Guide.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Third-party risk assessments shall evaluate: (1) Data access scope (CUI categories handled), (2) Security documentation (FedRAMP authorization, SOC 2 Type II, CMMC level), (3) Incident history, (4) Subcontractor reliance, (5) Data residency and jurisdiction, (6) Contractual security requirements and right-to-audit clauses. For current third-party assessment status, see the vendor risk register maintained by Procurement. FedRAMP marketplace verification: FedRAMP Marketplace.</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational systems regardless of impact level. It applies to all personnel with system ownership, security, or authorization responsibilities. Third-party providers handling CUI are subject to the risk assessment requirements in RMP04.001. For FedRAMP-specific risk management requirements applicable to cloud service providers, refer to the Cloud Security Policy and FedRAMP Risk Management documentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Risk_Management_Policy_POL-RM-2026-009.docx</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>RMP04.002</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>RMP04.002 Supply Chain Risk Management</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>This policy establishes the risk management requirements for all information systems and organizational operations. It defines the processes for identifying, assessing, accepting, and mitigating risks to organizational information assets. This policy implements NIST RMF requirements and supports continuous ATO maintenance. For the NIST Risk Management Framework overview, see NIST RMF Quick Start Guide.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Third-party risk assessments shall evaluate: (1) Data access scope (CUI categories handled), (2) Security documentation (FedRAMP authorization, SOC 2 Type II, CMMC level), (3) Incident history, (4) Subcontractor reliance, (5) Data residency and jurisdiction, (6) Contractual security requirements and right-to-audit clauses. For current third-party assessment status, see the vendor risk register maintained by Procurement. FedRAMP marketplace verification: FedRAMP Marketplace.</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational systems regardless of impact level. It applies to all personnel with system ownership, security, or authorization responsibilities. Third-party providers handling CUI are subject to the risk assessment requirements in RMP04.001. For FedRAMP-specific risk management requirements applicable to cloud service providers, refer to the Cloud Security Policy and FedRAMP Risk Management documentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Risk_Management_Policy_POL-RM-2026-009.docx</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>RMP02.001</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>The organization shall assess supply chain risks for critical technology acquisitions per NIST SP 800-161r1. Findings shall be documented in the risk register per RMP02.001. SR-2 Not Implemented CISO Source Type Integration CISA AIS Automated Indicator Sharing STIX/TAXII feed. Integrated to SIEM. FBI InfraGard Threat intelligence reports Manual review monthly by Threat Intel team. MS-ISAC Sector-specific intelligence Email distribution and portal access. Internal SOC Incident-derived IOCs Automated export from SIEM to risk register. POA&amp;M ID Finding Source Weakness Milestone Due Date Status POA-2026-001 Annual Assessment</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>This policy establishes the risk management requirements for all information systems and organizational operations. It defines the processes for identifying, assessing, accepting, and mitigating risks to organizational information assets. This policy implements NIST RMF requirements and supports continuous ATO maintenance. For the NIST Risk Management Framework overview, see NIST RMF Quick Start Guide.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Third-party risk assessments shall evaluate: (1) Data access scope (CUI categories handled), (2) Security documentation (FedRAMP authorization, SOC 2 Type II, CMMC level), (3) Incident history, (4) Subcontractor reliance, (5) Data residency and jurisdiction, (6) Contractual security requirements and right-to-audit clauses. For current third-party assessment status, see the vendor risk register maintained by Procurement. FedRAMP marketplace verification: FedRAMP Marketplace.</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational systems regardless of impact level. It applies to all personnel with system ownership, security, or authorization responsibilities. Third-party providers handling CUI are subject to the risk assessment requirements in RMP04.001. For FedRAMP-specific risk management requirements applicable to cloud service providers, refer to the Cloud Security Policy and FedRAMP Risk Management documentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Risk_Management_Policy_POL-RM-2026-009.docx</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>CFG03.002</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>CFG03.002 Drift Detection not implemented Deploy Defender baselines 06/30/2026 In Progress POA-2026-002 Audit Finding</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>This policy establishes the risk management requirements for all information systems and organizational operations. It defines the processes for identifying, assessing, accepting, and mitigating risks to organizational information assets. This policy implements NIST RMF requirements and supports continuous ATO maintenance. For the NIST Risk Management Framework overview, see NIST RMF Quick Start Guide.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Third-party risk assessments shall evaluate: (1) Data access scope (CUI categories handled), (2) Security documentation (FedRAMP authorization, SOC 2 Type II, CMMC level), (3) Incident history, (4) Subcontractor reliance, (5) Data residency and jurisdiction, (6) Contractual security requirements and right-to-audit clauses. For current third-party assessment status, see the vendor risk register maintained by Procurement. FedRAMP marketplace verification: FedRAMP Marketplace.</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational systems regardless of impact level. It applies to all personnel with system ownership, security, or authorization responsibilities. Third-party providers handling CUI are subject to the risk assessment requirements in RMP04.001. For FedRAMP-specific risk management requirements applicable to cloud service providers, refer to the Cloud Security Policy and FedRAMP Risk Management documentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Risk_Management_Policy_POL-RM-2026-009.docx</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>ACC03.002</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>ACC03.002 Session termination not enforced GPO configuration update 04/15/2026 In Progress POA-2026-003 IR After-Action</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>This policy establishes the risk management requirements for all information systems and organizational operations. It defines the processes for identifying, assessing, accepting, and mitigating risks to organizational information assets. This policy implements NIST RMF requirements and supports continuous ATO maintenance. For the NIST Risk Management Framework overview, see NIST RMF Quick Start Guide.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Third-party risk assessments shall evaluate: (1) Data access scope (CUI categories handled), (2) Security documentation (FedRAMP authorization, SOC 2 Type II, CMMC level), (3) Incident history, (4) Subcontractor reliance, (5) Data residency and jurisdiction, (6) Contractual security requirements and right-to-audit clauses. For current third-party assessment status, see the vendor risk register maintained by Procurement. FedRAMP marketplace verification: FedRAMP Marketplace.</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational systems regardless of impact level. It applies to all personnel with system ownership, security, or authorization responsibilities. Third-party providers handling CUI are subject to the risk assessment requirements in RMP04.001. For FedRAMP-specific risk management requirements applicable to cloud service providers, refer to the Cloud Security Policy and FedRAMP Risk Management documentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Risk_Management_Policy_POL-RM-2026-009.docx</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>DLP04.002</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>DLP04.002 Print controls not deployed Purview print DLP config 09/30/2026 Not Started Version Date Author Changes 2.0 02/01/2026 K. Williams, CISO</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>This policy establishes the risk management requirements for all information systems and organizational operations. It defines the processes for identifying, assessing, accepting, and mitigating risks to organizational information assets. This policy implements NIST RMF requirements and supports continuous ATO maintenance. For the NIST Risk Management Framework overview, see NIST RMF Quick Start Guide.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Third-party risk assessments shall evaluate: (1) Data access scope (CUI categories handled), (2) Security documentation (FedRAMP authorization, SOC 2 Type II, CMMC level), (3) Incident history, (4) Subcontractor reliance, (5) Data residency and jurisdiction, (6) Contractual security requirements and right-to-audit clauses. For current third-party assessment status, see the vendor risk register maintained by Procurement. FedRAMP marketplace verification: FedRAMP Marketplace.</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational systems regardless of impact level. It applies to all personnel with system ownership, security, or authorization responsibilities. Third-party providers handling CUI are subject to the risk assessment requirements in RMP04.001. For FedRAMP-specific risk management requirements applicable to cloud service providers, refer to the Cloud Security Policy and FedRAMP Risk Management documentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Risk_Management_Policy_POL-RM-2026-009.docx</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Appendix G - Revision History</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>RMP04.002</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Added SCRM requirements (RMP04.002), Appendix B threat sources 1.2 08/01/2025 K. Williams, CISO Updated POA&amp;M template to align with FedRAMP Rev 5 1.1 02/15/2025 L. Chen, ISSO Added third-party risk assessment criteria (Appendix F) 1.0 01/15/2025 L. Chen, ISSO Initial release</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>This policy establishes the risk management requirements for all information systems and organizational operations. It defines the processes for identifying, assessing, accepting, and mitigating risks to organizational information assets. This policy implements NIST RMF requirements and supports continuous ATO maintenance. For the NIST Risk Management Framework overview, see NIST RMF Quick Start Guide.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Third-party risk assessments shall evaluate: (1) Data access scope (CUI categories handled), (2) Security documentation (FedRAMP authorization, SOC 2 Type II, CMMC level), (3) Incident history, (4) Subcontractor reliance, (5) Data residency and jurisdiction, (6) Contractual security requirements and right-to-audit clauses. For current third-party assessment status, see the vendor risk register maintained by Procurement. FedRAMP marketplace verification: FedRAMP Marketplace.</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>This policy applies to all organizational systems regardless of impact level. It applies to all personnel with system ownership, security, or authorization responsibilities. Third-party providers handling CUI are subject to the risk assessment requirements in RMP04.001. For FedRAMP-specific risk management requirements applicable to cloud service providers, refer to the Cloud Security Policy and FedRAMP Risk Management documentation.</t>
         </is>
       </c>
     </row>
